--- a/research/traditional_assets/database/data/pakistan/pakistan_diversified.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1648684342779273</v>
+        <v>0.1644222658185213</v>
       </c>
       <c r="C2">
-        <v>60.85593301169556</v>
+        <v>60.4174128496883</v>
       </c>
       <c r="D2">
-        <v>45.35593301169556</v>
+        <v>45.50684006387576</v>
       </c>
       <c r="E2">
-        <v>-14.5427214187462</v>
+        <v>-13.95329420455874</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.589427214187462</v>
       </c>
       <c r="G2">
         <v>15.5</v>
@@ -1445,28 +1445,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02964818887362934</v>
       </c>
       <c r="N2">
-        <v>16.74833333333333</v>
+        <v>16.71868514445971</v>
       </c>
       <c r="O2">
-        <v>4.857016666666667</v>
+        <v>4.848418691893314</v>
       </c>
       <c r="P2">
-        <v>11.89131666666667</v>
+        <v>11.87026645256639</v>
       </c>
       <c r="Q2">
-        <v>12.39131666666667</v>
+        <v>12.37026645256639</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1648684342779273</v>
+        <v>0.1657223594126478</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7334302216662548</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>564.9024095441521</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1644222658185213</v>
+        <v>0.1639760973591153</v>
       </c>
       <c r="C3">
-        <v>60.4174128496883</v>
+        <v>59.97990022779035</v>
       </c>
       <c r="D3">
-        <v>45.50684006387576</v>
+        <v>45.65875465616528</v>
       </c>
       <c r="E3">
-        <v>-13.95329420455874</v>
+        <v>-13.36386699037127</v>
       </c>
       <c r="F3">
-        <v>0.589427214187462</v>
+        <v>1.178854428374924</v>
       </c>
       <c r="G3">
         <v>15.5</v>
@@ -1527,28 +1527,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M3">
-        <v>0.02964818887362934</v>
+        <v>0.05929637774725868</v>
       </c>
       <c r="N3">
-        <v>16.71868514445971</v>
+        <v>16.68903695558608</v>
       </c>
       <c r="O3">
-        <v>4.848418691893314</v>
+        <v>4.839820717119962</v>
       </c>
       <c r="P3">
-        <v>11.87026645256639</v>
+        <v>11.84921623846611</v>
       </c>
       <c r="Q3">
-        <v>12.37026645256639</v>
+        <v>12.34921623846611</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1657223594126478</v>
+        <v>0.166593711590934</v>
       </c>
       <c r="T3">
-        <v>0.7334302216662548</v>
+        <v>0.7387593031186203</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>564.9024095441521</v>
+        <v>282.451204772076</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1639760973591153</v>
+        <v>0.1635299288997094</v>
       </c>
       <c r="C4">
-        <v>59.97990022779035</v>
+        <v>59.54340527015313</v>
       </c>
       <c r="D4">
-        <v>45.65875465616528</v>
+        <v>45.81168691271552</v>
       </c>
       <c r="E4">
-        <v>-13.36386699037127</v>
+        <v>-12.77443977618381</v>
       </c>
       <c r="F4">
-        <v>1.178854428374924</v>
+        <v>1.768281642562386</v>
       </c>
       <c r="G4">
         <v>15.5</v>
@@ -1609,28 +1609,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M4">
-        <v>0.05929637774725868</v>
+        <v>0.088944566620888</v>
       </c>
       <c r="N4">
-        <v>16.68903695558608</v>
+        <v>16.65938876671245</v>
       </c>
       <c r="O4">
-        <v>4.839820717119962</v>
+        <v>4.831222742346609</v>
       </c>
       <c r="P4">
-        <v>11.84921623846611</v>
+        <v>11.82816602436584</v>
       </c>
       <c r="Q4">
-        <v>12.34921623846611</v>
+        <v>12.32816602436584</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.166593711590934</v>
+        <v>0.1674830297935148</v>
       </c>
       <c r="T4">
-        <v>0.7387593031186203</v>
+        <v>0.7441982625390756</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>282.451204772076</v>
+        <v>188.3008031813841</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1635299288997094</v>
+        <v>0.1630837604403033</v>
       </c>
       <c r="C5">
-        <v>59.54340527015313</v>
+        <v>59.10793823702582</v>
       </c>
       <c r="D5">
-        <v>45.81168691271552</v>
+        <v>45.96564709377567</v>
       </c>
       <c r="E5">
-        <v>-12.77443977618381</v>
+        <v>-12.18501256199635</v>
       </c>
       <c r="F5">
-        <v>1.768281642562386</v>
+        <v>2.357708856749848</v>
       </c>
       <c r="G5">
         <v>15.5</v>
@@ -1691,28 +1691,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M5">
-        <v>0.088944566620888</v>
+        <v>0.1185927554945174</v>
       </c>
       <c r="N5">
-        <v>16.65938876671245</v>
+        <v>16.62974057783882</v>
       </c>
       <c r="O5">
-        <v>4.831222742346609</v>
+        <v>4.822624767573257</v>
       </c>
       <c r="P5">
-        <v>11.82816602436584</v>
+        <v>11.80711581026556</v>
       </c>
       <c r="Q5">
-        <v>12.32816602436584</v>
+        <v>12.30711581026556</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1674830297935148</v>
+        <v>0.1683908754586493</v>
       </c>
       <c r="T5">
-        <v>0.7441982625390756</v>
+        <v>0.7497505336141237</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>188.3008031813841</v>
+        <v>141.225602386038</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1630837604403033</v>
+        <v>0.1626375919808973</v>
       </c>
       <c r="C6">
-        <v>59.10793823702582</v>
+        <v>58.67350952704984</v>
       </c>
       <c r="D6">
-        <v>45.96564709377567</v>
+        <v>46.12064559798716</v>
       </c>
       <c r="E6">
-        <v>-12.18501256199635</v>
+        <v>-11.59558534780889</v>
       </c>
       <c r="F6">
-        <v>2.357708856749848</v>
+        <v>2.94713607093731</v>
       </c>
       <c r="G6">
         <v>15.5</v>
@@ -1773,28 +1773,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M6">
-        <v>0.1185927554945174</v>
+        <v>0.1482409443681467</v>
       </c>
       <c r="N6">
-        <v>16.62974057783882</v>
+        <v>16.60009238896519</v>
       </c>
       <c r="O6">
-        <v>4.822624767573257</v>
+        <v>4.814026792799904</v>
       </c>
       <c r="P6">
-        <v>11.80711581026556</v>
+        <v>11.78606559616528</v>
       </c>
       <c r="Q6">
-        <v>12.30711581026556</v>
+        <v>12.28606559616528</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1683908754586493</v>
+        <v>0.1693178336641025</v>
       </c>
       <c r="T6">
-        <v>0.7497505336141237</v>
+        <v>0.7554196946065412</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>141.225602386038</v>
+        <v>112.9804819088304</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1626375919808973</v>
+        <v>0.1621914235214914</v>
       </c>
       <c r="C7">
-        <v>58.67350952704984</v>
+        <v>58.24012967960028</v>
       </c>
       <c r="D7">
-        <v>46.12064559798716</v>
+        <v>46.27669296472505</v>
       </c>
       <c r="E7">
-        <v>-11.59558534780889</v>
+        <v>-11.00615813362143</v>
       </c>
       <c r="F7">
-        <v>2.94713607093731</v>
+        <v>3.536563285124772</v>
       </c>
       <c r="G7">
         <v>15.5</v>
@@ -1855,28 +1855,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M7">
-        <v>0.1482409443681467</v>
+        <v>0.177889133241776</v>
       </c>
       <c r="N7">
-        <v>16.60009238896519</v>
+        <v>16.57044420009156</v>
       </c>
       <c r="O7">
-        <v>4.814026792799904</v>
+        <v>4.805428818026551</v>
       </c>
       <c r="P7">
-        <v>11.78606559616528</v>
+        <v>11.76501538206501</v>
       </c>
       <c r="Q7">
-        <v>12.28606559616528</v>
+        <v>12.26501538206501</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1693178336641025</v>
+        <v>0.1702645143845653</v>
       </c>
       <c r="T7">
-        <v>0.7554196946065412</v>
+        <v>0.7612094760456061</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>112.9804819088304</v>
+        <v>94.15040159069201</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1621914235214914</v>
+        <v>0.1617452550620854</v>
       </c>
       <c r="C8">
-        <v>58.24012967960028</v>
+        <v>57.80780937717459</v>
       </c>
       <c r="D8">
-        <v>46.27669296472505</v>
+        <v>46.43379987648682</v>
       </c>
       <c r="E8">
-        <v>-11.00615813362143</v>
+        <v>-10.41673091943397</v>
       </c>
       <c r="F8">
-        <v>3.536563285124771</v>
+        <v>4.125990499312233</v>
       </c>
       <c r="G8">
         <v>15.5</v>
@@ -1937,28 +1937,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M8">
-        <v>0.177889133241776</v>
+        <v>0.2075373221154053</v>
       </c>
       <c r="N8">
-        <v>16.57044420009156</v>
+        <v>16.54079601121793</v>
       </c>
       <c r="O8">
-        <v>4.805428818026551</v>
+        <v>4.796830843253199</v>
       </c>
       <c r="P8">
-        <v>11.76501538206501</v>
+        <v>11.74396516796473</v>
       </c>
       <c r="Q8">
-        <v>12.26501538206501</v>
+        <v>12.24396516796473</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1702645143845653</v>
+        <v>0.1712315538301993</v>
       </c>
       <c r="T8">
-        <v>0.7612094760456061</v>
+        <v>0.767123768913468</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>94.15040159069204</v>
+        <v>80.70034422059317</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1617452550620854</v>
+        <v>0.1612990866026794</v>
       </c>
       <c r="C9">
-        <v>57.80780937717461</v>
+        <v>57.37655944783055</v>
       </c>
       <c r="D9">
-        <v>46.43379987648684</v>
+        <v>46.59197716133025</v>
       </c>
       <c r="E9">
-        <v>-10.41673091943396</v>
+        <v>-9.827303705246504</v>
       </c>
       <c r="F9">
-        <v>4.125990499312234</v>
+        <v>4.715417713499696</v>
       </c>
       <c r="G9">
         <v>15.5</v>
@@ -2019,28 +2019,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M9">
-        <v>0.2075373221154054</v>
+        <v>0.2371855109890347</v>
       </c>
       <c r="N9">
-        <v>16.54079601121793</v>
+        <v>16.5111478223443</v>
       </c>
       <c r="O9">
-        <v>4.796830843253199</v>
+        <v>4.788232868479846</v>
       </c>
       <c r="P9">
-        <v>11.74396516796473</v>
+        <v>11.72291495386445</v>
       </c>
       <c r="Q9">
-        <v>12.24396516796473</v>
+        <v>12.22291495386445</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1712315538301993</v>
+        <v>0.1722196158724776</v>
       </c>
       <c r="T9">
-        <v>0.767123768913468</v>
+        <v>0.7731666333654137</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>80.70034422059315</v>
+        <v>70.61280119301901</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1612990866026794</v>
+        <v>0.1608529181432734</v>
       </c>
       <c r="C10">
-        <v>57.37655944783055</v>
+        <v>56.94639086767382</v>
       </c>
       <c r="D10">
-        <v>46.59197716133025</v>
+        <v>46.75123579536098</v>
       </c>
       <c r="E10">
-        <v>-9.827303705246504</v>
+        <v>-9.237876491059041</v>
       </c>
       <c r="F10">
-        <v>4.715417713499696</v>
+        <v>5.304844927687157</v>
       </c>
       <c r="G10">
         <v>15.5</v>
@@ -2101,28 +2101,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M10">
-        <v>0.2371855109890347</v>
+        <v>0.266833699862664</v>
       </c>
       <c r="N10">
-        <v>16.5111478223443</v>
+        <v>16.48149963347067</v>
       </c>
       <c r="O10">
-        <v>4.788232868479846</v>
+        <v>4.779634893706493</v>
       </c>
       <c r="P10">
-        <v>11.72291495386445</v>
+        <v>11.70186473976418</v>
       </c>
       <c r="Q10">
-        <v>12.22291495386445</v>
+        <v>12.20186473976418</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1722196158724776</v>
+        <v>0.1732293935640367</v>
       </c>
       <c r="T10">
-        <v>0.7731666333654137</v>
+        <v>0.7793423080250946</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>70.61280119301901</v>
+        <v>62.76693439379468</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1608529181432734</v>
+        <v>0.1604067496838674</v>
       </c>
       <c r="C11">
-        <v>56.94639086767382</v>
+        <v>56.51731476339691</v>
       </c>
       <c r="D11">
-        <v>46.75123579536098</v>
+        <v>46.91158690527153</v>
       </c>
       <c r="E11">
-        <v>-9.237876491059041</v>
+        <v>-8.648449276871581</v>
       </c>
       <c r="F11">
-        <v>5.304844927687157</v>
+        <v>5.894272141874619</v>
       </c>
       <c r="G11">
         <v>15.5</v>
@@ -2183,28 +2183,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M11">
-        <v>0.266833699862664</v>
+        <v>0.2964818887362933</v>
       </c>
       <c r="N11">
-        <v>16.48149963347067</v>
+        <v>16.45185144459704</v>
       </c>
       <c r="O11">
-        <v>4.779634893706493</v>
+        <v>4.771036918933143</v>
       </c>
       <c r="P11">
-        <v>11.70186473976418</v>
+        <v>11.6808145256639</v>
       </c>
       <c r="Q11">
-        <v>12.20186473976418</v>
+        <v>12.1808145256639</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1732293935640367</v>
+        <v>0.1742616107598527</v>
       </c>
       <c r="T11">
-        <v>0.7793423080250946</v>
+        <v>0.7856552198994351</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>62.76693439379468</v>
+        <v>56.49024095441523</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1604067496838674</v>
+        <v>0.1599605812244614</v>
       </c>
       <c r="C12">
-        <v>56.51731476339691</v>
+        <v>56.08934241487064</v>
       </c>
       <c r="D12">
-        <v>46.91158690527153</v>
+        <v>47.07304177093273</v>
       </c>
       <c r="E12">
-        <v>-8.648449276871579</v>
+        <v>-8.059022062684118</v>
       </c>
       <c r="F12">
-        <v>5.89427214187462</v>
+        <v>6.483699356062082</v>
       </c>
       <c r="G12">
         <v>15.5</v>
@@ -2265,28 +2265,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M12">
-        <v>0.2964818887362933</v>
+        <v>0.3261300776099227</v>
       </c>
       <c r="N12">
-        <v>16.45185144459704</v>
+        <v>16.42220325572341</v>
       </c>
       <c r="O12">
-        <v>4.771036918933143</v>
+        <v>4.76243894415979</v>
       </c>
       <c r="P12">
-        <v>11.6808145256639</v>
+        <v>11.65976431156362</v>
       </c>
       <c r="Q12">
-        <v>12.1808145256639</v>
+        <v>12.15976431156362</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1742616107598527</v>
+        <v>0.1753170238477094</v>
       </c>
       <c r="T12">
-        <v>0.7856552198994351</v>
+        <v>0.792109994961963</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>56.49024095441523</v>
+        <v>51.35476450401384</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1599605812244614</v>
+        <v>0.1595144127650554</v>
       </c>
       <c r="C13">
-        <v>56.08934241487064</v>
+        <v>55.66248525778912</v>
       </c>
       <c r="D13">
-        <v>47.07304177093273</v>
+        <v>47.23561182803866</v>
       </c>
       <c r="E13">
-        <v>-8.059022062684118</v>
+        <v>-7.469594848496656</v>
       </c>
       <c r="F13">
-        <v>6.483699356062082</v>
+        <v>7.073126570249543</v>
       </c>
       <c r="G13">
         <v>15.5</v>
@@ -2347,28 +2347,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M13">
-        <v>0.3261300776099227</v>
+        <v>0.355778266483552</v>
       </c>
       <c r="N13">
-        <v>16.42220325572341</v>
+        <v>16.39255506684978</v>
       </c>
       <c r="O13">
-        <v>4.76243894415979</v>
+        <v>4.753840969386437</v>
       </c>
       <c r="P13">
-        <v>11.65976431156362</v>
+        <v>11.63871409746335</v>
       </c>
       <c r="Q13">
-        <v>12.15976431156362</v>
+        <v>12.13871409746335</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1753170238477094</v>
+        <v>0.1763964235966539</v>
       </c>
       <c r="T13">
-        <v>0.792109994961963</v>
+        <v>0.7987114694577302</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>51.35476450401384</v>
+        <v>47.07520079534602</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1595144127650554</v>
+        <v>0.1590682443056494</v>
       </c>
       <c r="C14">
-        <v>55.66248525778912</v>
+        <v>55.23675488636981</v>
       </c>
       <c r="D14">
-        <v>47.23561182803866</v>
+        <v>47.39930867080682</v>
       </c>
       <c r="E14">
-        <v>-7.469594848496656</v>
+        <v>-6.880167634309193</v>
       </c>
       <c r="F14">
-        <v>7.073126570249543</v>
+        <v>7.662553784437006</v>
       </c>
       <c r="G14">
         <v>15.5</v>
@@ -2429,28 +2429,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M14">
-        <v>0.355778266483552</v>
+        <v>0.3854264553571814</v>
       </c>
       <c r="N14">
-        <v>16.39255506684978</v>
+        <v>16.36290687797615</v>
       </c>
       <c r="O14">
-        <v>4.753840969386437</v>
+        <v>4.745242994613085</v>
       </c>
       <c r="P14">
-        <v>11.63871409746335</v>
+        <v>11.61766388336307</v>
       </c>
       <c r="Q14">
-        <v>12.13871409746335</v>
+        <v>12.11766388336307</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1763964235966539</v>
+        <v>0.1775006371329304</v>
       </c>
       <c r="T14">
-        <v>0.7987114694577302</v>
+        <v>0.8054647019878829</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>47.07520079534602</v>
+        <v>43.45403150339632</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1590682443056494</v>
+        <v>0.1586220758462434</v>
       </c>
       <c r="C15">
-        <v>55.23675488636981</v>
+        <v>54.81216305610997</v>
       </c>
       <c r="D15">
-        <v>47.39930867080682</v>
+        <v>47.56414405473443</v>
       </c>
       <c r="E15">
-        <v>-6.880167634309193</v>
+        <v>-6.290740420121731</v>
       </c>
       <c r="F15">
-        <v>7.662553784437006</v>
+        <v>8.251980998624468</v>
       </c>
       <c r="G15">
         <v>15.5</v>
@@ -2511,28 +2511,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M15">
-        <v>0.3854264553571814</v>
+        <v>0.4150746442308108</v>
       </c>
       <c r="N15">
-        <v>16.36290687797615</v>
+        <v>16.33325868910253</v>
       </c>
       <c r="O15">
-        <v>4.745242994613085</v>
+        <v>4.736645019839732</v>
       </c>
       <c r="P15">
-        <v>11.61766388336307</v>
+        <v>11.59661366926279</v>
       </c>
       <c r="Q15">
-        <v>12.11766388336307</v>
+        <v>12.09661366926279</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1775006371329304</v>
+        <v>0.1786305300537714</v>
       </c>
       <c r="T15">
-        <v>0.8054647019878829</v>
+        <v>0.8123749864373413</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>43.45403150339632</v>
+        <v>40.35017211029658</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1586220758462434</v>
+        <v>0.1581759073868375</v>
       </c>
       <c r="C16">
-        <v>54.81216305610997</v>
+        <v>54.38872168660063</v>
       </c>
       <c r="D16">
-        <v>47.56414405473443</v>
+        <v>47.73012989941257</v>
       </c>
       <c r="E16">
-        <v>-6.290740420121731</v>
+        <v>-5.701313205934268</v>
       </c>
       <c r="F16">
-        <v>8.251980998624468</v>
+        <v>8.841408212811931</v>
       </c>
       <c r="G16">
         <v>15.5</v>
@@ -2593,28 +2593,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M16">
-        <v>0.4150746442308108</v>
+        <v>0.4447228331044401</v>
       </c>
       <c r="N16">
-        <v>16.33325868910253</v>
+        <v>16.3036105002289</v>
       </c>
       <c r="O16">
-        <v>4.736645019839732</v>
+        <v>4.728047045066379</v>
       </c>
       <c r="P16">
-        <v>11.59661366926279</v>
+        <v>11.57556345516252</v>
       </c>
       <c r="Q16">
-        <v>12.09661366926279</v>
+        <v>12.07556345516252</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1786305300537714</v>
+        <v>0.179787008690397</v>
       </c>
       <c r="T16">
-        <v>0.8123749864373413</v>
+        <v>0.8194478658150224</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>40.35017211029658</v>
+        <v>37.66016063627681</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1581759073868375</v>
+        <v>0.1577297389274315</v>
       </c>
       <c r="C17">
-        <v>54.38872168660064</v>
+        <v>53.96644286440007</v>
       </c>
       <c r="D17">
-        <v>47.73012989941257</v>
+        <v>47.89727829139947</v>
       </c>
       <c r="E17">
-        <v>-5.701313205934269</v>
+        <v>-5.111885991746806</v>
       </c>
       <c r="F17">
-        <v>8.841408212811929</v>
+        <v>9.430835426999392</v>
       </c>
       <c r="G17">
         <v>15.5</v>
@@ -2675,28 +2675,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M17">
-        <v>0.44472283310444</v>
+        <v>0.4743710219780694</v>
       </c>
       <c r="N17">
-        <v>16.3036105002289</v>
+        <v>16.27396231135527</v>
       </c>
       <c r="O17">
-        <v>4.728047045066379</v>
+        <v>4.719449070293027</v>
       </c>
       <c r="P17">
-        <v>11.57556345516252</v>
+        <v>11.55451324106224</v>
       </c>
       <c r="Q17">
-        <v>12.07556345516252</v>
+        <v>12.05451324106224</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.179787008690397</v>
+        <v>0.1809710225326565</v>
       </c>
       <c r="T17">
-        <v>0.8194478658150224</v>
+        <v>0.8266891470826482</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>37.66016063627681</v>
+        <v>35.30640059650951</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1577297389274315</v>
+        <v>0.1572835704680255</v>
       </c>
       <c r="C18">
-        <v>53.96644286440007</v>
+        <v>53.54533884596741</v>
       </c>
       <c r="D18">
-        <v>47.89727829139947</v>
+        <v>48.06560148715427</v>
       </c>
       <c r="E18">
-        <v>-5.111885991746806</v>
+        <v>-4.522458777559345</v>
       </c>
       <c r="F18">
-        <v>9.430835426999392</v>
+        <v>10.02026264118685</v>
       </c>
       <c r="G18">
         <v>15.5</v>
@@ -2757,28 +2757,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M18">
-        <v>0.4743710219780694</v>
+        <v>0.5040192108516988</v>
       </c>
       <c r="N18">
-        <v>16.27396231135527</v>
+        <v>16.24431412248164</v>
       </c>
       <c r="O18">
-        <v>4.719449070293027</v>
+        <v>4.710851095519674</v>
       </c>
       <c r="P18">
-        <v>11.55451324106224</v>
+        <v>11.53346302696196</v>
       </c>
       <c r="Q18">
-        <v>12.05451324106224</v>
+        <v>12.03346302696196</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1809710225326565</v>
+        <v>0.1821835668289464</v>
       </c>
       <c r="T18">
-        <v>0.8266891470826482</v>
+        <v>0.8341049170555181</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>35.30640059650951</v>
+        <v>33.22955350259718</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1572835704680255</v>
+        <v>0.1568374020086195</v>
       </c>
       <c r="C19">
-        <v>53.54533884596741</v>
+        <v>53.12542206065865</v>
       </c>
       <c r="D19">
-        <v>48.06560148715427</v>
+        <v>48.23511191603297</v>
       </c>
       <c r="E19">
-        <v>-4.522458777559345</v>
+        <v>-3.933031563371882</v>
       </c>
       <c r="F19">
-        <v>10.02026264118685</v>
+        <v>10.60968985537432</v>
       </c>
       <c r="G19">
         <v>15.5</v>
@@ -2839,28 +2839,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M19">
-        <v>0.5040192108516988</v>
+        <v>0.5336673997253281</v>
       </c>
       <c r="N19">
-        <v>16.24431412248164</v>
+        <v>16.21466593360801</v>
       </c>
       <c r="O19">
-        <v>4.710851095519674</v>
+        <v>4.702253120746322</v>
       </c>
       <c r="P19">
-        <v>11.53346302696196</v>
+        <v>11.51241281286168</v>
       </c>
       <c r="Q19">
-        <v>12.03346302696196</v>
+        <v>12.01241281286168</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1821835668289464</v>
+        <v>0.1834256853763652</v>
       </c>
       <c r="T19">
-        <v>0.8341049170555181</v>
+        <v>0.8417015594667505</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>33.22955350259718</v>
+        <v>31.38346719689734</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1568374020086195</v>
+        <v>0.1563912335492135</v>
       </c>
       <c r="C20">
-        <v>53.12542206065864</v>
+        <v>52.70670511378611</v>
       </c>
       <c r="D20">
-        <v>48.23511191603296</v>
+        <v>48.40582218334789</v>
       </c>
       <c r="E20">
-        <v>-3.933031563371884</v>
+        <v>-3.343604349184421</v>
       </c>
       <c r="F20">
-        <v>10.60968985537431</v>
+        <v>11.19911706956178</v>
       </c>
       <c r="G20">
         <v>15.5</v>
@@ -2921,28 +2921,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M20">
-        <v>0.5336673997253281</v>
+        <v>0.5633155885989574</v>
       </c>
       <c r="N20">
-        <v>16.21466593360801</v>
+        <v>16.18501774473438</v>
       </c>
       <c r="O20">
-        <v>4.702253120746322</v>
+        <v>4.693655145972969</v>
       </c>
       <c r="P20">
-        <v>11.51241281286168</v>
+        <v>11.49136259876141</v>
       </c>
       <c r="Q20">
-        <v>12.01241281286168</v>
+        <v>11.99136259876141</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1834256853763652</v>
+        <v>0.1846984735175475</v>
       </c>
       <c r="T20">
-        <v>0.8417015594667505</v>
+        <v>0.8494857732955444</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>31.38346719689734</v>
+        <v>29.7317057654817</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1563912335492135</v>
+        <v>0.1559450650898075</v>
       </c>
       <c r="C21">
-        <v>52.70670511378611</v>
+        <v>52.28920078974324</v>
       </c>
       <c r="D21">
-        <v>48.40582218334789</v>
+        <v>48.57774507349249</v>
       </c>
       <c r="E21">
-        <v>-3.343604349184421</v>
+        <v>-2.75417713499696</v>
       </c>
       <c r="F21">
-        <v>11.19911706956178</v>
+        <v>11.78854428374924</v>
       </c>
       <c r="G21">
         <v>15.5</v>
@@ -3003,28 +3003,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M21">
-        <v>0.5633155885989574</v>
+        <v>0.5929637774725867</v>
       </c>
       <c r="N21">
-        <v>16.18501774473438</v>
+        <v>16.15536955586075</v>
       </c>
       <c r="O21">
-        <v>4.693655145972969</v>
+        <v>4.685057171199617</v>
       </c>
       <c r="P21">
-        <v>11.49136259876141</v>
+        <v>11.47031238466113</v>
       </c>
       <c r="Q21">
-        <v>11.99136259876141</v>
+        <v>11.97031238466113</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1846984735175475</v>
+        <v>0.1860030813622594</v>
       </c>
       <c r="T21">
-        <v>0.8494857732955444</v>
+        <v>0.8574645924700581</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>29.7317057654817</v>
+        <v>28.24512047720761</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1559450650898075</v>
+        <v>0.1554988966304015</v>
       </c>
       <c r="C22">
-        <v>52.28920078974324</v>
+        <v>51.8729220551961</v>
       </c>
       <c r="D22">
-        <v>48.57774507349249</v>
+        <v>48.7508935531328</v>
       </c>
       <c r="E22">
-        <v>-2.75417713499696</v>
+        <v>-2.164749920809497</v>
       </c>
       <c r="F22">
-        <v>11.78854428374924</v>
+        <v>12.3779714979367</v>
       </c>
       <c r="G22">
         <v>15.5</v>
@@ -3085,28 +3085,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M22">
-        <v>0.5929637774725867</v>
+        <v>0.6226119663462161</v>
       </c>
       <c r="N22">
-        <v>16.15536955586075</v>
+        <v>16.12572136698712</v>
       </c>
       <c r="O22">
-        <v>4.685057171199617</v>
+        <v>4.676459196426264</v>
       </c>
       <c r="P22">
-        <v>11.47031238466113</v>
+        <v>11.44926217056085</v>
       </c>
       <c r="Q22">
-        <v>11.97031238466113</v>
+        <v>11.94926217056085</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1860030813622594</v>
+        <v>0.1873407172536728</v>
       </c>
       <c r="T22">
-        <v>0.8574645924700581</v>
+        <v>0.8656454070667113</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>28.24512047720761</v>
+        <v>26.90011474019772</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1554988966304015</v>
+        <v>0.1550527281709955</v>
       </c>
       <c r="C23">
-        <v>51.8729220551961</v>
+        <v>51.4578820623434</v>
       </c>
       <c r="D23">
-        <v>48.7508935531328</v>
+        <v>48.92528077446757</v>
       </c>
       <c r="E23">
-        <v>-2.164749920809498</v>
+        <v>-1.575322706622035</v>
       </c>
       <c r="F23">
-        <v>12.3779714979367</v>
+        <v>12.96739871212416</v>
       </c>
       <c r="G23">
         <v>15.5</v>
@@ -3167,28 +3167,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M23">
-        <v>0.622611966346216</v>
+        <v>0.6522601552198454</v>
       </c>
       <c r="N23">
-        <v>16.12572136698712</v>
+        <v>16.09607317811349</v>
       </c>
       <c r="O23">
-        <v>4.676459196426264</v>
+        <v>4.667861221652911</v>
       </c>
       <c r="P23">
-        <v>11.44926217056085</v>
+        <v>11.42821195646058</v>
       </c>
       <c r="Q23">
-        <v>11.94926217056085</v>
+        <v>11.92821195646058</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1873407172536728</v>
+        <v>0.1887126515012763</v>
       </c>
       <c r="T23">
-        <v>0.8656454070667113</v>
+        <v>0.8740359861402017</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>26.90011474019773</v>
+        <v>25.67738225200692</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1550527281709955</v>
+        <v>0.1546065597115896</v>
       </c>
       <c r="C24">
-        <v>51.4578820623434</v>
+        <v>51.04409415224678</v>
       </c>
       <c r="D24">
-        <v>48.92528077446757</v>
+        <v>49.10092007855841</v>
       </c>
       <c r="E24">
-        <v>-1.575322706622035</v>
+        <v>-0.9858954924345724</v>
       </c>
       <c r="F24">
-        <v>12.96739871212416</v>
+        <v>13.55682592631163</v>
       </c>
       <c r="G24">
         <v>15.5</v>
@@ -3249,28 +3249,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M24">
-        <v>0.6522601552198454</v>
+        <v>0.6819083440934748</v>
       </c>
       <c r="N24">
-        <v>16.09607317811349</v>
+        <v>16.06642498923986</v>
       </c>
       <c r="O24">
-        <v>4.667861221652911</v>
+        <v>4.659263246879559</v>
       </c>
       <c r="P24">
-        <v>11.42821195646058</v>
+        <v>11.4071617423603</v>
       </c>
       <c r="Q24">
-        <v>11.92821195646058</v>
+        <v>11.9071617423603</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1887126515012763</v>
+        <v>0.1901202204046618</v>
       </c>
       <c r="T24">
-        <v>0.8740359861402017</v>
+        <v>0.8826445023324844</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>25.67738225200692</v>
+        <v>24.56097432800661</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1546065597115896</v>
+        <v>0.1541603912521836</v>
       </c>
       <c r="C25">
-        <v>51.04409415224678</v>
+        <v>50.63157185823314</v>
       </c>
       <c r="D25">
-        <v>49.10092007855841</v>
+        <v>49.27782499873224</v>
       </c>
       <c r="E25">
-        <v>-0.9858954924345724</v>
+        <v>-0.3964682782471112</v>
       </c>
       <c r="F25">
-        <v>13.55682592631163</v>
+        <v>14.14625314049909</v>
       </c>
       <c r="G25">
         <v>15.5</v>
@@ -3331,28 +3331,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M25">
-        <v>0.6819083440934748</v>
+        <v>0.7115565329671041</v>
       </c>
       <c r="N25">
-        <v>16.06642498923986</v>
+        <v>16.03677680036623</v>
       </c>
       <c r="O25">
-        <v>4.659263246879559</v>
+        <v>4.650665272106206</v>
       </c>
       <c r="P25">
-        <v>11.4071617423603</v>
+        <v>11.38611152826002</v>
       </c>
       <c r="Q25">
-        <v>11.9071617423603</v>
+        <v>11.88611152826002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1901202204046618</v>
+        <v>0.1915648305949784</v>
       </c>
       <c r="T25">
-        <v>0.8826445023324844</v>
+        <v>0.8914795584245636</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>24.56097432800661</v>
+        <v>23.53760039767301</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1541603912521836</v>
+        <v>0.1537142227927775</v>
       </c>
       <c r="C26">
-        <v>50.63157185823314</v>
+        <v>50.22032890937056</v>
       </c>
       <c r="D26">
-        <v>49.27782499873224</v>
+        <v>49.45600926405712</v>
       </c>
       <c r="E26">
-        <v>-0.3964682782471129</v>
+        <v>0.1929589359403501</v>
       </c>
       <c r="F26">
-        <v>14.14625314049909</v>
+        <v>14.73568035468655</v>
       </c>
       <c r="G26">
         <v>15.5</v>
@@ -3413,28 +3413,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M26">
-        <v>0.711556532967104</v>
+        <v>0.7412047218407334</v>
       </c>
       <c r="N26">
-        <v>16.03677680036623</v>
+        <v>16.0071286114926</v>
       </c>
       <c r="O26">
-        <v>4.650665272106206</v>
+        <v>4.642067297332853</v>
       </c>
       <c r="P26">
-        <v>11.38611152826002</v>
+        <v>11.36506131415975</v>
       </c>
       <c r="Q26">
-        <v>11.88611152826002</v>
+        <v>11.86506131415975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1915648305949784</v>
+        <v>0.1930479637237034</v>
       </c>
       <c r="T26">
-        <v>0.8914795584245636</v>
+        <v>0.9005502160124318</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>23.53760039767301</v>
+        <v>22.59609638176608</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1537142227927775</v>
+        <v>0.1532680543333716</v>
       </c>
       <c r="C27">
-        <v>50.22032890937056</v>
+        <v>49.81037923402017</v>
       </c>
       <c r="D27">
-        <v>49.45600926405712</v>
+        <v>49.63548680289419</v>
       </c>
       <c r="E27">
-        <v>0.1929589359403501</v>
+        <v>0.7823861501278131</v>
       </c>
       <c r="F27">
-        <v>14.73568035468655</v>
+        <v>15.32510756887401</v>
       </c>
       <c r="G27">
         <v>15.5</v>
@@ -3495,28 +3495,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M27">
-        <v>0.7412047218407334</v>
+        <v>0.7708529107143628</v>
       </c>
       <c r="N27">
-        <v>16.0071286114926</v>
+        <v>15.97748042261897</v>
       </c>
       <c r="O27">
-        <v>4.642067297332853</v>
+        <v>4.633469322559502</v>
       </c>
       <c r="P27">
-        <v>11.36506131415975</v>
+        <v>11.34401110005947</v>
       </c>
       <c r="Q27">
-        <v>11.86506131415975</v>
+        <v>11.84401110005947</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1930479637237034</v>
+        <v>0.1945711815315832</v>
       </c>
       <c r="T27">
-        <v>0.9005502160124318</v>
+        <v>0.9098660265080802</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>22.59609638176608</v>
+        <v>21.72701575169816</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1532680543333716</v>
+        <v>0.1528218858739656</v>
       </c>
       <c r="C28">
-        <v>49.81037923402017</v>
+        <v>49.40173696346551</v>
       </c>
       <c r="D28">
-        <v>49.63548680289419</v>
+        <v>49.81627174652698</v>
       </c>
       <c r="E28">
-        <v>0.7823861501278131</v>
+        <v>1.371813364315274</v>
       </c>
       <c r="F28">
-        <v>15.32510756887401</v>
+        <v>15.91453478306147</v>
       </c>
       <c r="G28">
         <v>15.5</v>
@@ -3577,28 +3577,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M28">
-        <v>0.7708529107143628</v>
+        <v>0.8005010995879921</v>
       </c>
       <c r="N28">
-        <v>15.97748042261897</v>
+        <v>15.94783223374534</v>
       </c>
       <c r="O28">
-        <v>4.633469322559502</v>
+        <v>4.624871347786149</v>
       </c>
       <c r="P28">
-        <v>11.34401110005947</v>
+        <v>11.32296088595919</v>
       </c>
       <c r="Q28">
-        <v>11.84401110005947</v>
+        <v>11.82296088595919</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1945711815315832</v>
+        <v>0.1961361313341994</v>
       </c>
       <c r="T28">
-        <v>0.9098660265080802</v>
+        <v>0.9194370646885408</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>21.72701575169816</v>
+        <v>20.92231146459823</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1528218858739656</v>
+        <v>0.1523757174145596</v>
       </c>
       <c r="C29">
-        <v>49.40173696346551</v>
+        <v>48.99441643562146</v>
       </c>
       <c r="D29">
-        <v>49.81627174652698</v>
+        <v>49.99837843287039</v>
       </c>
       <c r="E29">
-        <v>1.371813364315274</v>
+        <v>1.961240578502737</v>
       </c>
       <c r="F29">
-        <v>15.91453478306147</v>
+        <v>16.50396199724894</v>
       </c>
       <c r="G29">
         <v>15.5</v>
@@ -3659,28 +3659,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M29">
-        <v>0.8005010995879921</v>
+        <v>0.8301492884616215</v>
       </c>
       <c r="N29">
-        <v>15.94783223374534</v>
+        <v>15.91818404487171</v>
       </c>
       <c r="O29">
-        <v>4.624871347786149</v>
+        <v>4.616273373012796</v>
       </c>
       <c r="P29">
-        <v>11.32296088595919</v>
+        <v>11.30191067185892</v>
       </c>
       <c r="Q29">
-        <v>11.82296088595919</v>
+        <v>11.80191067185892</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1961361313341994</v>
+        <v>0.1977445519646661</v>
       </c>
       <c r="T29">
-        <v>0.9194370646885408</v>
+        <v>0.929273965040681</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>20.92231146459823</v>
+        <v>20.17508605514829</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1523757174145596</v>
+        <v>0.1519295489551536</v>
       </c>
       <c r="C30">
-        <v>48.99441643562146</v>
+        <v>48.58843219882493</v>
       </c>
       <c r="D30">
-        <v>49.99837843287039</v>
+        <v>50.18182141026134</v>
       </c>
       <c r="E30">
-        <v>1.961240578502737</v>
+        <v>2.5506677926902</v>
       </c>
       <c r="F30">
-        <v>16.50396199724894</v>
+        <v>17.0933892114364</v>
       </c>
       <c r="G30">
         <v>15.5</v>
@@ -3741,28 +3741,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M30">
-        <v>0.8301492884616215</v>
+        <v>0.8597974773352508</v>
       </c>
       <c r="N30">
-        <v>15.91818404487171</v>
+        <v>15.88853585599808</v>
       </c>
       <c r="O30">
-        <v>4.616273373012796</v>
+        <v>4.607675398239444</v>
       </c>
       <c r="P30">
-        <v>11.30191067185892</v>
+        <v>11.28086045775864</v>
       </c>
       <c r="Q30">
-        <v>11.80191067185892</v>
+        <v>11.78086045775864</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1977445519646661</v>
+        <v>0.1993982802185262</v>
       </c>
       <c r="T30">
-        <v>0.929273965040681</v>
+        <v>0.9393879611773885</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>20.17508605514829</v>
+        <v>19.47939343255697</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1519295489551536</v>
+        <v>0.1514833804957476</v>
       </c>
       <c r="C31">
-        <v>48.58843219882494</v>
+        <v>48.18379901570927</v>
       </c>
       <c r="D31">
-        <v>50.18182141026134</v>
+        <v>50.36661544133313</v>
       </c>
       <c r="E31">
-        <v>2.550667792690197</v>
+        <v>3.14009500687766</v>
       </c>
       <c r="F31">
-        <v>17.0933892114364</v>
+        <v>17.68281642562386</v>
       </c>
       <c r="G31">
         <v>15.5</v>
@@ -3823,28 +3823,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M31">
-        <v>0.8597974773352507</v>
+        <v>0.88944566620888</v>
       </c>
       <c r="N31">
-        <v>15.88853585599808</v>
+        <v>15.85888766712445</v>
       </c>
       <c r="O31">
-        <v>4.607675398239444</v>
+        <v>4.599077423466092</v>
       </c>
       <c r="P31">
-        <v>11.28086045775864</v>
+        <v>11.25981024365836</v>
       </c>
       <c r="Q31">
-        <v>11.78086045775864</v>
+        <v>11.75981024365836</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1993982802185262</v>
+        <v>0.201099257851068</v>
       </c>
       <c r="T31">
-        <v>0.9393879611773885</v>
+        <v>0.9497909286322875</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>19.47939343255697</v>
+        <v>18.83008031813841</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1514833804957476</v>
+        <v>0.1510372120363416</v>
       </c>
       <c r="C32">
-        <v>48.18379901570927</v>
+        <v>47.78053186716446</v>
       </c>
       <c r="D32">
-        <v>50.36661544133313</v>
+        <v>50.55277550697578</v>
       </c>
       <c r="E32">
-        <v>3.14009500687766</v>
+        <v>3.729522221065123</v>
       </c>
       <c r="F32">
-        <v>17.68281642562386</v>
+        <v>18.27224363981132</v>
       </c>
       <c r="G32">
         <v>15.5</v>
@@ -3905,28 +3905,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M32">
-        <v>0.88944566620888</v>
+        <v>0.9190938550825094</v>
       </c>
       <c r="N32">
-        <v>15.85888766712445</v>
+        <v>15.82923947825083</v>
       </c>
       <c r="O32">
-        <v>4.599077423466092</v>
+        <v>4.590479448692739</v>
       </c>
       <c r="P32">
-        <v>11.25981024365836</v>
+        <v>11.23876002955809</v>
       </c>
       <c r="Q32">
-        <v>11.75981024365836</v>
+        <v>11.73876002955809</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.201099257851068</v>
+        <v>0.2028495391831038</v>
       </c>
       <c r="T32">
-        <v>0.9497909286322875</v>
+        <v>0.9604954313757345</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>18.83008031813841</v>
+        <v>18.222658372392</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1510372120363416</v>
+        <v>0.1505910435769356</v>
       </c>
       <c r="C33">
-        <v>47.78053186716446</v>
+        <v>47.37864595638564</v>
       </c>
       <c r="D33">
-        <v>50.55277550697578</v>
+        <v>50.74031681038443</v>
       </c>
       <c r="E33">
-        <v>3.729522221065123</v>
+        <v>4.318949435252586</v>
       </c>
       <c r="F33">
-        <v>18.27224363981132</v>
+        <v>18.86167085399878</v>
       </c>
       <c r="G33">
         <v>15.5</v>
@@ -3987,28 +3987,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M33">
-        <v>0.9190938550825094</v>
+        <v>0.9487420439561388</v>
       </c>
       <c r="N33">
-        <v>15.82923947825083</v>
+        <v>15.7995912893772</v>
       </c>
       <c r="O33">
-        <v>4.590479448692739</v>
+        <v>4.581881473919386</v>
       </c>
       <c r="P33">
-        <v>11.23876002955809</v>
+        <v>11.21770981545781</v>
       </c>
       <c r="Q33">
-        <v>11.73876002955809</v>
+        <v>11.71770981545781</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2028495391831038</v>
+        <v>0.2046512993778465</v>
       </c>
       <c r="T33">
-        <v>0.9604954313757345</v>
+        <v>0.9715147724351652</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>18.222658372392</v>
+        <v>17.65320029825475</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1505910435769356</v>
+        <v>0.1501448751175296</v>
       </c>
       <c r="C34">
-        <v>47.37864595638564</v>
+        <v>46.97815671301205</v>
       </c>
       <c r="D34">
-        <v>50.74031681038443</v>
+        <v>50.9292547811983</v>
       </c>
       <c r="E34">
-        <v>4.318949435252586</v>
+        <v>4.908376649440045</v>
       </c>
       <c r="F34">
-        <v>18.86167085399878</v>
+        <v>19.45109806818624</v>
       </c>
       <c r="G34">
         <v>15.5</v>
@@ -4069,28 +4069,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M34">
-        <v>0.9487420439561388</v>
+        <v>0.978390232829768</v>
       </c>
       <c r="N34">
-        <v>15.7995912893772</v>
+        <v>15.76994310050357</v>
       </c>
       <c r="O34">
-        <v>4.581881473919386</v>
+        <v>4.573283499146035</v>
       </c>
       <c r="P34">
-        <v>11.21770981545781</v>
+        <v>11.19665960135753</v>
       </c>
       <c r="Q34">
-        <v>11.71770981545781</v>
+        <v>11.69665960135753</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2046512993778465</v>
+        <v>0.2065068434589995</v>
       </c>
       <c r="T34">
-        <v>0.9715147724351652</v>
+        <v>0.9828630490486086</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.65320029825475</v>
+        <v>17.11825483467128</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1501448751175296</v>
+        <v>0.1496987066581236</v>
       </c>
       <c r="C35">
-        <v>46.97815671301205</v>
+        <v>46.57907979735869</v>
       </c>
       <c r="D35">
-        <v>50.9292547811983</v>
+        <v>51.11960507973239</v>
       </c>
       <c r="E35">
-        <v>4.908376649440045</v>
+        <v>5.497803863627508</v>
       </c>
       <c r="F35">
-        <v>19.45109806818624</v>
+        <v>20.04052528237371</v>
       </c>
       <c r="G35">
         <v>15.5</v>
@@ -4151,28 +4151,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M35">
-        <v>0.978390232829768</v>
+        <v>1.008038421703398</v>
       </c>
       <c r="N35">
-        <v>15.76994310050357</v>
+        <v>15.74029491162994</v>
       </c>
       <c r="O35">
-        <v>4.573283499146035</v>
+        <v>4.564685524372682</v>
       </c>
       <c r="P35">
-        <v>11.19665960135753</v>
+        <v>11.17560938725726</v>
       </c>
       <c r="Q35">
-        <v>11.69665960135753</v>
+        <v>11.67560938725726</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2065068434589995</v>
+        <v>0.2084186161486722</v>
       </c>
       <c r="T35">
-        <v>0.9828630490486086</v>
+        <v>0.9945552128321564</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>17.11825483467128</v>
+        <v>16.61477675129859</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1496987066581236</v>
+        <v>0.1492525381987177</v>
       </c>
       <c r="C36">
-        <v>46.57907979735869</v>
+        <v>46.18143110474327</v>
       </c>
       <c r="D36">
-        <v>51.11960507973239</v>
+        <v>51.31138360130444</v>
       </c>
       <c r="E36">
-        <v>5.497803863627508</v>
+        <v>6.087231077814971</v>
       </c>
       <c r="F36">
-        <v>20.04052528237371</v>
+        <v>20.62995249656117</v>
       </c>
       <c r="G36">
         <v>15.5</v>
@@ -4233,28 +4233,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M36">
-        <v>1.008038421703398</v>
+        <v>1.037686610577027</v>
       </c>
       <c r="N36">
-        <v>15.74029491162994</v>
+        <v>15.71064672275631</v>
       </c>
       <c r="O36">
-        <v>4.564685524372682</v>
+        <v>4.556087549599329</v>
       </c>
       <c r="P36">
-        <v>11.17560938725726</v>
+        <v>11.15455917315698</v>
       </c>
       <c r="Q36">
-        <v>11.67560938725726</v>
+        <v>11.65455917315698</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2084186161486722</v>
+        <v>0.2103892126134118</v>
       </c>
       <c r="T36">
-        <v>0.9945552128321564</v>
+        <v>1.006607135501352</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.61477675129859</v>
+        <v>16.14006884411863</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1492525381987177</v>
+        <v>0.1488063697393117</v>
       </c>
       <c r="C37">
-        <v>46.18143110474327</v>
+        <v>45.78522676991111</v>
       </c>
       <c r="D37">
-        <v>51.31138360130444</v>
+        <v>51.50460648065975</v>
       </c>
       <c r="E37">
-        <v>6.087231077814971</v>
+        <v>6.676658292002434</v>
       </c>
       <c r="F37">
-        <v>20.62995249656117</v>
+        <v>21.21937971074863</v>
       </c>
       <c r="G37">
         <v>15.5</v>
@@ -4315,28 +4315,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M37">
-        <v>1.037686610577027</v>
+        <v>1.067334799450656</v>
       </c>
       <c r="N37">
-        <v>15.71064672275631</v>
+        <v>15.68099853388268</v>
       </c>
       <c r="O37">
-        <v>4.556087549599329</v>
+        <v>4.547489574825977</v>
       </c>
       <c r="P37">
-        <v>11.15455917315698</v>
+        <v>11.1335089590567</v>
       </c>
       <c r="Q37">
-        <v>11.65455917315698</v>
+        <v>11.6335089590567</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2103892126134118</v>
+        <v>0.2124213902176745</v>
       </c>
       <c r="T37">
-        <v>1.006607135501352</v>
+        <v>1.01903568075396</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>16.14006884411863</v>
+        <v>15.69173359844867</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1488063697393117</v>
+        <v>0.1483602012799057</v>
       </c>
       <c r="C38">
-        <v>45.78522676991111</v>
+        <v>45.39048317156005</v>
       </c>
       <c r="D38">
-        <v>51.50460648065974</v>
+        <v>51.69929009649614</v>
       </c>
       <c r="E38">
-        <v>6.676658292002431</v>
+        <v>7.266085506189894</v>
       </c>
       <c r="F38">
-        <v>21.21937971074863</v>
+        <v>21.80880692493609</v>
       </c>
       <c r="G38">
         <v>15.5</v>
@@ -4397,28 +4397,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M38">
-        <v>1.067334799450656</v>
+        <v>1.096982988324285</v>
       </c>
       <c r="N38">
-        <v>15.68099853388268</v>
+        <v>15.65135034500905</v>
       </c>
       <c r="O38">
-        <v>4.547489574825977</v>
+        <v>4.538891600052624</v>
       </c>
       <c r="P38">
-        <v>11.1335089590567</v>
+        <v>11.11245874495643</v>
       </c>
       <c r="Q38">
-        <v>11.6335089590567</v>
+        <v>11.61245874495643</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2124213902176745</v>
+        <v>0.2145180813966757</v>
       </c>
       <c r="T38">
-        <v>1.01903568075396</v>
+        <v>1.031858782998714</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.69173359844867</v>
+        <v>15.26763269038249</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1483602012799057</v>
+        <v>0.1479140328204997</v>
       </c>
       <c r="C39">
-        <v>45.39048317156005</v>
+        <v>44.99721693696864</v>
       </c>
       <c r="D39">
-        <v>51.69929009649614</v>
+        <v>51.89545107609219</v>
       </c>
       <c r="E39">
-        <v>7.266085506189894</v>
+        <v>7.855512720377357</v>
       </c>
       <c r="F39">
-        <v>21.80880692493609</v>
+        <v>22.39823413912356</v>
       </c>
       <c r="G39">
         <v>15.5</v>
@@ -4479,28 +4479,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M39">
-        <v>1.096982988324285</v>
+        <v>1.126631177197915</v>
       </c>
       <c r="N39">
-        <v>15.65135034500905</v>
+        <v>15.62170215613542</v>
       </c>
       <c r="O39">
-        <v>4.538891600052624</v>
+        <v>4.530293625279271</v>
       </c>
       <c r="P39">
-        <v>11.11245874495643</v>
+        <v>11.09140853085615</v>
       </c>
       <c r="Q39">
-        <v>11.61245874495643</v>
+        <v>11.59140853085615</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2145180813966757</v>
+        <v>0.2166824077749995</v>
       </c>
       <c r="T39">
-        <v>1.031858782998714</v>
+        <v>1.045095533702976</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>15.26763269038249</v>
+        <v>14.86585288274085</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1479140328204997</v>
+        <v>0.1474678643610937</v>
       </c>
       <c r="C40">
-        <v>44.99721693696864</v>
+        <v>44.60544494672995</v>
       </c>
       <c r="D40">
-        <v>51.89545107609219</v>
+        <v>52.09310630004097</v>
       </c>
       <c r="E40">
-        <v>7.855512720377357</v>
+        <v>8.44493993456482</v>
       </c>
       <c r="F40">
-        <v>22.39823413912356</v>
+        <v>22.98766135331102</v>
       </c>
       <c r="G40">
         <v>15.5</v>
@@ -4561,28 +4561,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M40">
-        <v>1.126631177197915</v>
+        <v>1.156279366071544</v>
       </c>
       <c r="N40">
-        <v>15.62170215613542</v>
+        <v>15.59205396726179</v>
       </c>
       <c r="O40">
-        <v>4.530293625279271</v>
+        <v>4.521695650505919</v>
       </c>
       <c r="P40">
-        <v>11.09140853085615</v>
+        <v>11.07035831675587</v>
       </c>
       <c r="Q40">
-        <v>11.59140853085615</v>
+        <v>11.57035831675587</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2166824077749995</v>
+        <v>0.2189176956739241</v>
       </c>
       <c r="T40">
-        <v>1.045095533702976</v>
+        <v>1.058766276233608</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>14.86585288274085</v>
+        <v>14.48467716779877</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1474678643610937</v>
+        <v>0.1470216959016877</v>
       </c>
       <c r="C41">
-        <v>44.60544494672995</v>
+        <v>44.21518433959419</v>
       </c>
       <c r="D41">
-        <v>52.09310630004097</v>
+        <v>52.29227290709267</v>
       </c>
       <c r="E41">
-        <v>8.44493993456482</v>
+        <v>9.034367148752279</v>
       </c>
       <c r="F41">
-        <v>22.98766135331102</v>
+        <v>23.57708856749848</v>
       </c>
       <c r="G41">
         <v>15.5</v>
@@ -4643,28 +4643,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M41">
-        <v>1.156279366071544</v>
+        <v>1.185927554945173</v>
       </c>
       <c r="N41">
-        <v>15.59205396726179</v>
+        <v>15.56240577838816</v>
       </c>
       <c r="O41">
-        <v>4.521695650505919</v>
+        <v>4.513097675732566</v>
       </c>
       <c r="P41">
-        <v>11.07035831675587</v>
+        <v>11.04930810265559</v>
       </c>
       <c r="Q41">
-        <v>11.57035831675587</v>
+        <v>11.54930810265559</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2189176956739241</v>
+        <v>0.2212274931694796</v>
       </c>
       <c r="T41">
-        <v>1.058766276233608</v>
+        <v>1.072892710181927</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.48467716779877</v>
+        <v>14.12256023860381</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1470216959016877</v>
+        <v>0.1465755274422818</v>
       </c>
       <c r="C42">
-        <v>44.21518433959419</v>
+        <v>43.82645251742248</v>
       </c>
       <c r="D42">
-        <v>52.29227290709267</v>
+        <v>52.49296829910843</v>
       </c>
       <c r="E42">
-        <v>9.034367148752279</v>
+        <v>9.623794362939742</v>
       </c>
       <c r="F42">
-        <v>23.57708856749848</v>
+        <v>24.16651578168594</v>
       </c>
       <c r="G42">
         <v>15.5</v>
@@ -4725,28 +4725,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M42">
-        <v>1.185927554945173</v>
+        <v>1.215575743818803</v>
       </c>
       <c r="N42">
-        <v>15.56240577838816</v>
+        <v>15.53275758951453</v>
       </c>
       <c r="O42">
-        <v>4.513097675732566</v>
+        <v>4.504499700959214</v>
       </c>
       <c r="P42">
-        <v>11.04930810265559</v>
+        <v>11.02825788855532</v>
       </c>
       <c r="Q42">
-        <v>11.54930810265559</v>
+        <v>11.52825788855532</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2212274931694796</v>
+        <v>0.2236155888852233</v>
       </c>
       <c r="T42">
-        <v>1.072892710181927</v>
+        <v>1.087498006297986</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>14.12256023860381</v>
+        <v>13.77810754985737</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1465755274422818</v>
+        <v>0.1461293589828757</v>
       </c>
       <c r="C43">
-        <v>43.82645251742248</v>
+        <v>43.43926715025554</v>
       </c>
       <c r="D43">
-        <v>52.49296829910843</v>
+        <v>52.69521014612894</v>
       </c>
       <c r="E43">
-        <v>9.623794362939742</v>
+        <v>10.21322157712721</v>
       </c>
       <c r="F43">
-        <v>24.16651578168594</v>
+        <v>24.7559429958734</v>
       </c>
       <c r="G43">
         <v>15.5</v>
@@ -4807,28 +4807,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M43">
-        <v>1.215575743818803</v>
+        <v>1.245223932692432</v>
       </c>
       <c r="N43">
-        <v>15.53275758951453</v>
+        <v>15.5031094006409</v>
       </c>
       <c r="O43">
-        <v>4.504499700959214</v>
+        <v>4.495901726185862</v>
       </c>
       <c r="P43">
-        <v>11.02825788855532</v>
+        <v>11.00720767445504</v>
       </c>
       <c r="Q43">
-        <v>11.52825788855532</v>
+        <v>11.50720767445504</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2236155888852233</v>
+        <v>0.2260860327290961</v>
       </c>
       <c r="T43">
-        <v>1.087498006297986</v>
+        <v>1.102606933314598</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>13.77810754985737</v>
+        <v>13.45005737009886</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1461293589828758</v>
+        <v>0.1456831905234698</v>
       </c>
       <c r="C44">
-        <v>43.43926715025553</v>
+        <v>43.05364618149959</v>
       </c>
       <c r="D44">
-        <v>52.69521014612893</v>
+        <v>52.89901639156045</v>
       </c>
       <c r="E44">
-        <v>10.2132215771272</v>
+        <v>10.80264879131466</v>
       </c>
       <c r="F44">
-        <v>24.7559429958734</v>
+        <v>25.34537021006086</v>
       </c>
       <c r="G44">
         <v>15.5</v>
@@ -4889,28 +4889,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M44">
-        <v>1.245223932692432</v>
+        <v>1.274872121566061</v>
       </c>
       <c r="N44">
-        <v>15.5031094006409</v>
+        <v>15.47346121176727</v>
       </c>
       <c r="O44">
-        <v>4.495901726185862</v>
+        <v>4.487303751412509</v>
       </c>
       <c r="P44">
-        <v>11.00720767445504</v>
+        <v>10.98615746035476</v>
       </c>
       <c r="Q44">
-        <v>11.50720767445504</v>
+        <v>11.48615746035476</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2260860327290961</v>
+        <v>0.2286431588131048</v>
       </c>
       <c r="T44">
-        <v>1.102606933314598</v>
+        <v>1.118245998121268</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>13.45005737009886</v>
+        <v>13.1372653382361</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1456831905234698</v>
+        <v>0.1457056220640638</v>
       </c>
       <c r="C45">
-        <v>43.05364618149959</v>
+        <v>42.45393478563059</v>
       </c>
       <c r="D45">
-        <v>52.89901639156045</v>
+        <v>52.88873220987892</v>
       </c>
       <c r="E45">
-        <v>10.80264879131466</v>
+        <v>11.39207600550213</v>
       </c>
       <c r="F45">
-        <v>25.34537021006086</v>
+        <v>25.93479742424833</v>
       </c>
       <c r="G45">
         <v>15.5</v>
@@ -4971,45 +4971,45 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M45">
-        <v>1.274872121566061</v>
+        <v>1.343422506576063</v>
       </c>
       <c r="N45">
-        <v>15.47346121176727</v>
+        <v>15.40491082675727</v>
       </c>
       <c r="O45">
-        <v>4.487303751412509</v>
+        <v>4.467424139759609</v>
       </c>
       <c r="P45">
-        <v>10.98615746035476</v>
+        <v>10.93748668699766</v>
       </c>
       <c r="Q45">
-        <v>11.48615746035476</v>
+        <v>11.43748668699766</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2286431588131048</v>
+        <v>0.2312916108286853</v>
       </c>
       <c r="T45">
-        <v>1.118245998121268</v>
+        <v>1.134443600956746</v>
       </c>
       <c r="U45">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V45">
         <v>0.29</v>
       </c>
       <c r="W45">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y45">
-        <v>13.1372653382361</v>
+        <v>12.46691435594544</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1457056220640638</v>
+        <v>0.1452701036046578</v>
       </c>
       <c r="C46">
-        <v>42.45393478563059</v>
+        <v>42.06489715844233</v>
       </c>
       <c r="D46">
-        <v>52.88873220987892</v>
+        <v>53.08912179687812</v>
       </c>
       <c r="E46">
-        <v>11.39207600550213</v>
+        <v>11.98150321968959</v>
       </c>
       <c r="F46">
-        <v>25.93479742424833</v>
+        <v>26.52422463843579</v>
       </c>
       <c r="G46">
         <v>15.5</v>
@@ -5053,28 +5053,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M46">
-        <v>1.343422506576063</v>
+        <v>1.373954836270974</v>
       </c>
       <c r="N46">
-        <v>15.40491082675727</v>
+        <v>15.37437849706236</v>
       </c>
       <c r="O46">
-        <v>4.467424139759609</v>
+        <v>4.458569764148084</v>
       </c>
       <c r="P46">
-        <v>10.93748668699766</v>
+        <v>10.91580873291428</v>
       </c>
       <c r="Q46">
-        <v>11.43748668699766</v>
+        <v>11.41580873291428</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2312916108286853</v>
+        <v>0.2340363701902869</v>
       </c>
       <c r="T46">
-        <v>1.134443600956746</v>
+        <v>1.151230207531697</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>12.46691435594544</v>
+        <v>12.18987181470221</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1452701036046578</v>
+        <v>0.1448345851452518</v>
       </c>
       <c r="C47">
-        <v>42.06489715844233</v>
+        <v>41.67738381478924</v>
       </c>
       <c r="D47">
-        <v>53.08912179687812</v>
+        <v>53.29103566741249</v>
       </c>
       <c r="E47">
-        <v>11.98150321968959</v>
+        <v>12.57093043387705</v>
       </c>
       <c r="F47">
-        <v>26.52422463843579</v>
+        <v>27.11365185262325</v>
       </c>
       <c r="G47">
         <v>15.5</v>
@@ -5135,28 +5135,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M47">
-        <v>1.373954836270974</v>
+        <v>1.404487165965884</v>
       </c>
       <c r="N47">
-        <v>15.37437849706236</v>
+        <v>15.34384616736745</v>
       </c>
       <c r="O47">
-        <v>4.458569764148084</v>
+        <v>4.449715388536561</v>
       </c>
       <c r="P47">
-        <v>10.91580873291428</v>
+        <v>10.89413077883089</v>
       </c>
       <c r="Q47">
-        <v>11.41580873291428</v>
+        <v>11.39413077883089</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2340363701902869</v>
+        <v>0.2368827873060218</v>
       </c>
       <c r="T47">
-        <v>1.151230207531697</v>
+        <v>1.168638540276091</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>12.18987181470221</v>
+        <v>11.92487460133912</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1448345851452518</v>
+        <v>0.1443990666858458</v>
       </c>
       <c r="C48">
-        <v>41.67738381478924</v>
+        <v>41.29141221299443</v>
       </c>
       <c r="D48">
-        <v>53.29103566741249</v>
+        <v>53.49449127980514</v>
       </c>
       <c r="E48">
-        <v>12.57093043387705</v>
+        <v>13.16035764806451</v>
       </c>
       <c r="F48">
-        <v>27.11365185262325</v>
+        <v>27.70307906681071</v>
       </c>
       <c r="G48">
         <v>15.5</v>
@@ -5217,28 +5217,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M48">
-        <v>1.404487165965884</v>
+        <v>1.435019495660795</v>
       </c>
       <c r="N48">
-        <v>15.34384616736745</v>
+        <v>15.31331383767254</v>
       </c>
       <c r="O48">
-        <v>4.449715388536561</v>
+        <v>4.440861012925036</v>
       </c>
       <c r="P48">
-        <v>10.89413077883089</v>
+        <v>10.8724528247475</v>
       </c>
       <c r="Q48">
-        <v>11.39413077883089</v>
+        <v>11.3724528247475</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2368827873060218</v>
+        <v>0.2398366163883883</v>
       </c>
       <c r="T48">
-        <v>1.168638540276091</v>
+        <v>1.186703791237254</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.92487460133912</v>
+        <v>11.67115386514041</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1443990666858458</v>
+        <v>0.1439635482264398</v>
       </c>
       <c r="C49">
-        <v>41.29141221299443</v>
+        <v>40.90700007901381</v>
       </c>
       <c r="D49">
-        <v>53.49449127980514</v>
+        <v>53.69950636001199</v>
       </c>
       <c r="E49">
-        <v>13.16035764806451</v>
+        <v>13.74978486225198</v>
       </c>
       <c r="F49">
-        <v>27.70307906681071</v>
+        <v>28.29250628099818</v>
       </c>
       <c r="G49">
         <v>15.5</v>
@@ -5299,28 +5299,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M49">
-        <v>1.435019495660795</v>
+        <v>1.465551825355705</v>
       </c>
       <c r="N49">
-        <v>15.31331383767254</v>
+        <v>15.28278150797763</v>
       </c>
       <c r="O49">
-        <v>4.440861012925036</v>
+        <v>4.432006637313513</v>
       </c>
       <c r="P49">
-        <v>10.8724528247475</v>
+        <v>10.85077487066412</v>
       </c>
       <c r="Q49">
-        <v>11.3724528247475</v>
+        <v>11.35077487066412</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2398366163883883</v>
+        <v>0.242904054281615</v>
       </c>
       <c r="T49">
-        <v>1.186703791237254</v>
+        <v>1.205463859543077</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.67115386514041</v>
+        <v>11.42800482628332</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1439635482264398</v>
+        <v>0.1435280297670338</v>
       </c>
       <c r="C50">
-        <v>40.90700007901381</v>
+        <v>40.52416541158416</v>
       </c>
       <c r="D50">
-        <v>53.69950636001199</v>
+        <v>53.9060989067698</v>
       </c>
       <c r="E50">
-        <v>13.74978486225197</v>
+        <v>14.33921207643944</v>
       </c>
       <c r="F50">
-        <v>28.29250628099817</v>
+        <v>28.88193349518563</v>
       </c>
       <c r="G50">
         <v>15.5</v>
@@ -5381,28 +5381,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M50">
-        <v>1.465551825355705</v>
+        <v>1.496084155050616</v>
       </c>
       <c r="N50">
-        <v>15.28278150797763</v>
+        <v>15.25224917828272</v>
       </c>
       <c r="O50">
-        <v>4.432006637313513</v>
+        <v>4.423152261701988</v>
       </c>
       <c r="P50">
-        <v>10.85077487066412</v>
+        <v>10.82909691658073</v>
       </c>
       <c r="Q50">
-        <v>11.35077487066412</v>
+        <v>11.32909691658073</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.242904054281615</v>
+        <v>0.2460917838569291</v>
       </c>
       <c r="T50">
-        <v>1.205463859543077</v>
+        <v>1.22495961680207</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.42800482628332</v>
+        <v>11.19478023799183</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1435280297670338</v>
+        <v>0.1430925113076278</v>
       </c>
       <c r="C51">
-        <v>40.52416541158416</v>
+        <v>40.14292648749074</v>
       </c>
       <c r="D51">
-        <v>53.9060989067698</v>
+        <v>54.11428719686383</v>
       </c>
       <c r="E51">
-        <v>14.33921207643944</v>
+        <v>14.9286392906269</v>
       </c>
       <c r="F51">
-        <v>28.88193349518563</v>
+        <v>29.4713607093731</v>
       </c>
       <c r="G51">
         <v>15.5</v>
@@ -5463,28 +5463,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M51">
-        <v>1.496084155050616</v>
+        <v>1.526616484745526</v>
       </c>
       <c r="N51">
-        <v>15.25224917828272</v>
+        <v>15.22171684858781</v>
       </c>
       <c r="O51">
-        <v>4.423152261701988</v>
+        <v>4.414297886090464</v>
       </c>
       <c r="P51">
-        <v>10.82909691658073</v>
+        <v>10.80741896249734</v>
       </c>
       <c r="Q51">
-        <v>11.32909691658073</v>
+        <v>11.30741896249734</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2460917838569291</v>
+        <v>0.2494070226152557</v>
       </c>
       <c r="T51">
-        <v>1.22495961680207</v>
+        <v>1.245235204351422</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>11.19478023799183</v>
+        <v>10.97088463323199</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1430925113076278</v>
+        <v>0.1426569928482218</v>
       </c>
       <c r="C52">
-        <v>40.14292648749074</v>
+        <v>39.76330186695713</v>
       </c>
       <c r="D52">
-        <v>54.11428719686383</v>
+        <v>54.3240897905177</v>
       </c>
       <c r="E52">
-        <v>14.9286392906269</v>
+        <v>15.51806650481436</v>
       </c>
       <c r="F52">
-        <v>29.4713607093731</v>
+        <v>30.06078792356056</v>
       </c>
       <c r="G52">
         <v>15.5</v>
@@ -5545,28 +5545,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M52">
-        <v>1.526616484745526</v>
+        <v>1.557148814440437</v>
       </c>
       <c r="N52">
-        <v>15.22171684858781</v>
+        <v>15.1911845188929</v>
       </c>
       <c r="O52">
-        <v>4.414297886090464</v>
+        <v>4.40544351047894</v>
       </c>
       <c r="P52">
-        <v>10.80741896249734</v>
+        <v>10.78574100841396</v>
       </c>
       <c r="Q52">
-        <v>11.30741896249734</v>
+        <v>11.28574100841396</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2494070226152557</v>
+        <v>0.2528575772412691</v>
       </c>
       <c r="T52">
-        <v>1.245235204351422</v>
+        <v>1.266338366902789</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.97088463323199</v>
+        <v>10.75576924826666</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1426569928482218</v>
+        <v>0.1422214743888159</v>
       </c>
       <c r="C53">
-        <v>39.76330186695713</v>
+        <v>39.3853103991613</v>
       </c>
       <c r="D53">
-        <v>54.3240897905177</v>
+        <v>54.53552553690932</v>
       </c>
       <c r="E53">
-        <v>15.51806650481436</v>
+        <v>16.10749371900182</v>
       </c>
       <c r="F53">
-        <v>30.06078792356056</v>
+        <v>30.65021513774802</v>
       </c>
       <c r="G53">
         <v>15.5</v>
@@ -5627,28 +5627,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M53">
-        <v>1.557148814440437</v>
+        <v>1.587681144135348</v>
       </c>
       <c r="N53">
-        <v>15.1911845188929</v>
+        <v>15.16065218919799</v>
       </c>
       <c r="O53">
-        <v>4.40544351047894</v>
+        <v>4.396589134867416</v>
       </c>
       <c r="P53">
-        <v>10.78574100841396</v>
+        <v>10.76406305433057</v>
       </c>
       <c r="Q53">
-        <v>11.28574100841396</v>
+        <v>11.26406305433057</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2528575772412691</v>
+        <v>0.2564519049766997</v>
       </c>
       <c r="T53">
-        <v>1.266338366902789</v>
+        <v>1.288320827893796</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.75576924826666</v>
+        <v>10.54892753195384</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1422214743888159</v>
+        <v>0.1417859559294099</v>
       </c>
       <c r="C54">
-        <v>39.3853103991613</v>
+        <v>39.00897122788066</v>
       </c>
       <c r="D54">
-        <v>54.53552553690932</v>
+        <v>54.74861357981615</v>
       </c>
       <c r="E54">
-        <v>16.10749371900182</v>
+        <v>16.69692093318929</v>
       </c>
       <c r="F54">
-        <v>30.65021513774802</v>
+        <v>31.23964235193549</v>
       </c>
       <c r="G54">
         <v>15.5</v>
@@ -5709,28 +5709,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M54">
-        <v>1.587681144135348</v>
+        <v>1.618213473830258</v>
       </c>
       <c r="N54">
-        <v>15.16065218919799</v>
+        <v>15.13011985950308</v>
       </c>
       <c r="O54">
-        <v>4.396589134867416</v>
+        <v>4.387734759255892</v>
       </c>
       <c r="P54">
-        <v>10.76406305433057</v>
+        <v>10.74238510024719</v>
       </c>
       <c r="Q54">
-        <v>11.26406305433057</v>
+        <v>11.24238510024719</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2564519049766997</v>
+        <v>0.2601991828285317</v>
       </c>
       <c r="T54">
-        <v>1.288320827893796</v>
+        <v>1.311238712756761</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.54892753195384</v>
+        <v>10.3498911634264</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1417859559294099</v>
+        <v>0.1413504374700039</v>
       </c>
       <c r="C55">
-        <v>39.00897122788066</v>
+        <v>38.63430379727017</v>
       </c>
       <c r="D55">
-        <v>54.74861357981615</v>
+        <v>54.96337336339312</v>
       </c>
       <c r="E55">
-        <v>16.69692093318929</v>
+        <v>17.28634814737675</v>
       </c>
       <c r="F55">
-        <v>31.23964235193549</v>
+        <v>31.82906956612295</v>
       </c>
       <c r="G55">
         <v>15.5</v>
@@ -5791,28 +5791,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M55">
-        <v>1.618213473830258</v>
+        <v>1.648745803525169</v>
       </c>
       <c r="N55">
-        <v>15.13011985950308</v>
+        <v>15.09958752980817</v>
       </c>
       <c r="O55">
-        <v>4.387734759255892</v>
+        <v>4.378880383644368</v>
       </c>
       <c r="P55">
-        <v>10.74238510024719</v>
+        <v>10.7207071461638</v>
       </c>
       <c r="Q55">
-        <v>11.24238510024719</v>
+        <v>11.2207071461638</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2601991828285317</v>
+        <v>0.2641093858043562</v>
       </c>
       <c r="T55">
-        <v>1.311238712756761</v>
+        <v>1.335153027396376</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.3498911634264</v>
+        <v>10.15822651225184</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1413504374700039</v>
+        <v>0.1409149190105979</v>
       </c>
       <c r="C56">
-        <v>38.63430379727017</v>
+        <v>38.26132785777687</v>
       </c>
       <c r="D56">
-        <v>54.96337336339312</v>
+        <v>55.17982463808728</v>
       </c>
       <c r="E56">
-        <v>17.28634814737675</v>
+        <v>17.87577536156422</v>
       </c>
       <c r="F56">
-        <v>31.82906956612295</v>
+        <v>32.41849678031041</v>
       </c>
       <c r="G56">
         <v>15.5</v>
@@ -5873,28 +5873,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M56">
-        <v>1.648745803525169</v>
+        <v>1.679278133220079</v>
       </c>
       <c r="N56">
-        <v>15.09958752980817</v>
+        <v>15.06905520011325</v>
       </c>
       <c r="O56">
-        <v>4.378880383644368</v>
+        <v>4.370026008032844</v>
       </c>
       <c r="P56">
-        <v>10.7207071461638</v>
+        <v>10.69902919208041</v>
       </c>
       <c r="Q56">
-        <v>11.2207071461638</v>
+        <v>11.19902919208041</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2641093858043562</v>
+        <v>0.2681933755791064</v>
       </c>
       <c r="T56">
-        <v>1.335153027396376</v>
+        <v>1.360130200464419</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>10.15822651225184</v>
+        <v>9.973531484756352</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1409149190105979</v>
+        <v>0.1411553205511919</v>
       </c>
       <c r="C57">
-        <v>38.26132785777687</v>
+        <v>37.55221150998806</v>
       </c>
       <c r="D57">
-        <v>55.17982463808728</v>
+        <v>55.06013550448593</v>
       </c>
       <c r="E57">
-        <v>17.87577536156422</v>
+        <v>18.46520257575168</v>
       </c>
       <c r="F57">
-        <v>32.41849678031041</v>
+        <v>33.00792399449787</v>
       </c>
       <c r="G57">
         <v>15.5</v>
@@ -5955,45 +5955,45 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M57">
-        <v>1.679278133220079</v>
+        <v>1.765923933705636</v>
       </c>
       <c r="N57">
-        <v>15.06905520011325</v>
+        <v>14.9824093996277</v>
       </c>
       <c r="O57">
-        <v>4.370026008032844</v>
+        <v>4.344898725892032</v>
       </c>
       <c r="P57">
-        <v>10.69902919208041</v>
+        <v>10.63751067373567</v>
       </c>
       <c r="Q57">
-        <v>11.19902919208041</v>
+        <v>11.13751067373567</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2681933755791064</v>
+        <v>0.2724630012527089</v>
       </c>
       <c r="T57">
-        <v>1.360130200464419</v>
+        <v>1.386242699581009</v>
       </c>
       <c r="U57">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V57">
         <v>0.29</v>
       </c>
       <c r="W57">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>9.973531484756352</v>
+        <v>9.484175967980926</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1411553205511919</v>
+        <v>0.1407318720917859</v>
       </c>
       <c r="C58">
-        <v>37.55221150998806</v>
+        <v>37.17395684407207</v>
       </c>
       <c r="D58">
-        <v>55.06013550448593</v>
+        <v>55.27130805275741</v>
       </c>
       <c r="E58">
-        <v>18.46520257575168</v>
+        <v>19.05462978993913</v>
       </c>
       <c r="F58">
-        <v>33.00792399449787</v>
+        <v>33.59735120868533</v>
       </c>
       <c r="G58">
         <v>15.5</v>
@@ -6037,28 +6037,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M58">
-        <v>1.765923933705636</v>
+        <v>1.797458289664665</v>
       </c>
       <c r="N58">
-        <v>14.9824093996277</v>
+        <v>14.95087504366867</v>
       </c>
       <c r="O58">
-        <v>4.344898725892032</v>
+        <v>4.335753762663914</v>
       </c>
       <c r="P58">
-        <v>10.63751067373567</v>
+        <v>10.61512128100476</v>
       </c>
       <c r="Q58">
-        <v>11.13751067373567</v>
+        <v>11.11512128100476</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2724630012527089</v>
+        <v>0.276931214166944</v>
       </c>
       <c r="T58">
-        <v>1.386242699581009</v>
+        <v>1.413569733540231</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>9.484175967980926</v>
+        <v>9.317786915911086</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1407318720917859</v>
+        <v>0.1403084236323799</v>
       </c>
       <c r="C59">
-        <v>37.17395684407207</v>
+        <v>36.79732823789322</v>
       </c>
       <c r="D59">
-        <v>55.27130805275741</v>
+        <v>55.48410666076602</v>
       </c>
       <c r="E59">
-        <v>19.05462978993913</v>
+        <v>19.6440570041266</v>
       </c>
       <c r="F59">
-        <v>33.59735120868533</v>
+        <v>34.1867784228728</v>
       </c>
       <c r="G59">
         <v>15.5</v>
@@ -6119,28 +6119,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M59">
-        <v>1.797458289664665</v>
+        <v>1.828992645623695</v>
       </c>
       <c r="N59">
-        <v>14.95087504366867</v>
+        <v>14.91934068770964</v>
       </c>
       <c r="O59">
-        <v>4.335753762663914</v>
+        <v>4.326608799435795</v>
       </c>
       <c r="P59">
-        <v>10.61512128100476</v>
+        <v>10.59273188827385</v>
       </c>
       <c r="Q59">
-        <v>11.11512128100476</v>
+        <v>11.09273188827385</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.276931214166944</v>
+        <v>0.2816121991247141</v>
       </c>
       <c r="T59">
-        <v>1.413569733540231</v>
+        <v>1.442198054830845</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.317786915911086</v>
+        <v>9.157135417360893</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1403084236323799</v>
+        <v>0.1398849751729739</v>
       </c>
       <c r="C60">
-        <v>36.79732823789323</v>
+        <v>36.42234454538991</v>
       </c>
       <c r="D60">
-        <v>55.48410666076602</v>
+        <v>55.69855018245016</v>
       </c>
       <c r="E60">
-        <v>19.64405700412659</v>
+        <v>20.23348421831405</v>
       </c>
       <c r="F60">
-        <v>34.18677842287279</v>
+        <v>34.77620563706025</v>
       </c>
       <c r="G60">
         <v>15.5</v>
@@ -6201,28 +6201,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M60">
-        <v>1.828992645623694</v>
+        <v>1.860527001582723</v>
       </c>
       <c r="N60">
-        <v>14.91934068770964</v>
+        <v>14.88780633175061</v>
       </c>
       <c r="O60">
-        <v>4.326608799435795</v>
+        <v>4.317463836207677</v>
       </c>
       <c r="P60">
-        <v>10.59273188827385</v>
+        <v>10.57034249554293</v>
       </c>
       <c r="Q60">
-        <v>11.09273188827385</v>
+        <v>11.07034249554293</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2816121991247141</v>
+        <v>0.2865215248121315</v>
       </c>
       <c r="T60">
-        <v>1.442198054830845</v>
+        <v>1.47222287959905</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>9.157135417360895</v>
+        <v>9.00192973232088</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1398849751729739</v>
+        <v>0.1394615267135679</v>
       </c>
       <c r="C61">
-        <v>36.42234454538991</v>
+        <v>36.04902491310991</v>
       </c>
       <c r="D61">
-        <v>55.69855018245016</v>
+        <v>55.91465776435764</v>
       </c>
       <c r="E61">
-        <v>20.23348421831405</v>
+        <v>20.82291143250152</v>
       </c>
       <c r="F61">
-        <v>34.77620563706025</v>
+        <v>35.36563285124772</v>
       </c>
       <c r="G61">
         <v>15.5</v>
@@ -6283,28 +6283,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M61">
-        <v>1.860527001582723</v>
+        <v>1.892061357541753</v>
       </c>
       <c r="N61">
-        <v>14.88780633175061</v>
+        <v>14.85627197579158</v>
       </c>
       <c r="O61">
-        <v>4.317463836207677</v>
+        <v>4.308318872979559</v>
       </c>
       <c r="P61">
-        <v>10.57034249554293</v>
+        <v>10.54795310281202</v>
       </c>
       <c r="Q61">
-        <v>11.07034249554293</v>
+        <v>11.04795310281202</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2865215248121315</v>
+        <v>0.2916763167839198</v>
       </c>
       <c r="T61">
-        <v>1.47222287959905</v>
+        <v>1.503748945605664</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>9.00192973232088</v>
+        <v>8.851897570115531</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1394615267135679</v>
+        <v>0.139038078254162</v>
       </c>
       <c r="C62">
-        <v>36.04902491310991</v>
+        <v>35.67738878590895</v>
       </c>
       <c r="D62">
-        <v>55.91465776435764</v>
+        <v>56.13244885134412</v>
       </c>
       <c r="E62">
-        <v>20.82291143250152</v>
+        <v>21.41233864668898</v>
       </c>
       <c r="F62">
-        <v>35.36563285124772</v>
+        <v>35.95506006543518</v>
       </c>
       <c r="G62">
         <v>15.5</v>
@@ -6365,28 +6365,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M62">
-        <v>1.892061357541753</v>
+        <v>1.923595713500782</v>
       </c>
       <c r="N62">
-        <v>14.85627197579158</v>
+        <v>14.82473761983255</v>
       </c>
       <c r="O62">
-        <v>4.308318872979559</v>
+        <v>4.29917390975144</v>
       </c>
       <c r="P62">
-        <v>10.54795310281202</v>
+        <v>10.52556371008111</v>
       </c>
       <c r="Q62">
-        <v>11.04795310281202</v>
+        <v>11.02556371008111</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2916763167839198</v>
+        <v>0.2970954570619537</v>
       </c>
       <c r="T62">
-        <v>1.503748945605664</v>
+        <v>1.536891732945952</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.851897570115531</v>
+        <v>8.706784495195604</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.139038078254162</v>
+        <v>0.138614629794756</v>
       </c>
       <c r="C63">
-        <v>35.67738878590895</v>
+        <v>35.30745591278311</v>
       </c>
       <c r="D63">
-        <v>56.13244885134412</v>
+        <v>56.35194319240576</v>
       </c>
       <c r="E63">
-        <v>21.41233864668898</v>
+        <v>22.00176586087645</v>
       </c>
       <c r="F63">
-        <v>35.95506006543518</v>
+        <v>36.54448727962264</v>
       </c>
       <c r="G63">
         <v>15.5</v>
@@ -6447,28 +6447,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M63">
-        <v>1.923595713500782</v>
+        <v>1.955130069459811</v>
       </c>
       <c r="N63">
-        <v>14.82473761983255</v>
+        <v>14.79320326387352</v>
       </c>
       <c r="O63">
-        <v>4.29917390975144</v>
+        <v>4.290028946523321</v>
       </c>
       <c r="P63">
-        <v>10.52556371008111</v>
+        <v>10.5031743173502</v>
       </c>
       <c r="Q63">
-        <v>11.02556371008111</v>
+        <v>11.0031743173502</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2970954570619537</v>
+        <v>0.3027998152493578</v>
       </c>
       <c r="T63">
-        <v>1.536891732945952</v>
+        <v>1.571778877514675</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.706784495195604</v>
+        <v>8.566352487208578</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.138614629794756</v>
+        <v>0.13819118133535</v>
       </c>
       <c r="C64">
-        <v>35.30745591278311</v>
+        <v>34.93924635283864</v>
       </c>
       <c r="D64">
-        <v>56.35194319240576</v>
+        <v>56.57316084664875</v>
       </c>
       <c r="E64">
-        <v>22.00176586087645</v>
+        <v>22.59119307506391</v>
       </c>
       <c r="F64">
-        <v>36.54448727962264</v>
+        <v>37.1339144938101</v>
       </c>
       <c r="G64">
         <v>15.5</v>
@@ -6529,28 +6529,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M64">
-        <v>1.955130069459811</v>
+        <v>1.98666442541884</v>
       </c>
       <c r="N64">
-        <v>14.79320326387352</v>
+        <v>14.76166890791449</v>
       </c>
       <c r="O64">
-        <v>4.290028946523321</v>
+        <v>4.280883983295203</v>
       </c>
       <c r="P64">
-        <v>10.5031743173502</v>
+        <v>10.48078492461929</v>
       </c>
       <c r="Q64">
-        <v>11.0031743173502</v>
+        <v>10.98078492461929</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3027998152493578</v>
+        <v>0.3088125171225675</v>
       </c>
       <c r="T64">
-        <v>1.571778877514675</v>
+        <v>1.608551813681709</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.566352487208578</v>
+        <v>8.430378638205267</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.13819118133535</v>
+        <v>0.137767732875944</v>
       </c>
       <c r="C65">
-        <v>34.93924635283864</v>
+        <v>34.57278048140274</v>
       </c>
       <c r="D65">
-        <v>56.57316084664875</v>
+        <v>56.79612218940031</v>
       </c>
       <c r="E65">
-        <v>22.59119307506391</v>
+        <v>23.18062028925137</v>
       </c>
       <c r="F65">
-        <v>37.1339144938101</v>
+        <v>37.72334170799757</v>
       </c>
       <c r="G65">
         <v>15.5</v>
@@ -6611,28 +6611,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M65">
-        <v>1.98666442541884</v>
+        <v>2.01819878137787</v>
       </c>
       <c r="N65">
-        <v>14.76166890791449</v>
+        <v>14.73013455195547</v>
       </c>
       <c r="O65">
-        <v>4.280883983295203</v>
+        <v>4.271739020067085</v>
       </c>
       <c r="P65">
-        <v>10.48078492461929</v>
+        <v>10.45839553188838</v>
       </c>
       <c r="Q65">
-        <v>10.98078492461929</v>
+        <v>10.95839553188838</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3088125171225675</v>
+        <v>0.3151592579887333</v>
       </c>
       <c r="T65">
-        <v>1.608551813681709</v>
+        <v>1.64736769074691</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.430378638205267</v>
+        <v>8.29865397198331</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.137767732875944</v>
+        <v>0.137344284416538</v>
       </c>
       <c r="C66">
-        <v>34.57278048140274</v>
+        <v>34.20807899627955</v>
       </c>
       <c r="D66">
-        <v>56.79612218940031</v>
+        <v>57.02084791846458</v>
       </c>
       <c r="E66">
-        <v>23.18062028925137</v>
+        <v>23.77004750343883</v>
       </c>
       <c r="F66">
-        <v>37.72334170799757</v>
+        <v>38.31276892218503</v>
       </c>
       <c r="G66">
         <v>15.5</v>
@@ -6693,28 +6693,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M66">
-        <v>2.01819878137787</v>
+        <v>2.049733137336899</v>
       </c>
       <c r="N66">
-        <v>14.73013455195547</v>
+        <v>14.69860019599644</v>
       </c>
       <c r="O66">
-        <v>4.271739020067085</v>
+        <v>4.262594056838966</v>
       </c>
       <c r="P66">
-        <v>10.45839553188838</v>
+        <v>10.43600613915747</v>
       </c>
       <c r="Q66">
-        <v>10.95839553188838</v>
+        <v>10.93600613915747</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3151592579887333</v>
+        <v>0.3218686697615371</v>
       </c>
       <c r="T66">
-        <v>1.64736769074691</v>
+        <v>1.688401617930123</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.29865397198331</v>
+        <v>8.170982372414336</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.137344284416538</v>
+        <v>0.136920835957132</v>
       </c>
       <c r="C67">
-        <v>34.20807899627955</v>
+        <v>33.84516292415527</v>
       </c>
       <c r="D67">
-        <v>57.02084791846458</v>
+        <v>57.24735906052776</v>
       </c>
       <c r="E67">
-        <v>23.77004750343883</v>
+        <v>24.35947471762629</v>
       </c>
       <c r="F67">
-        <v>38.31276892218503</v>
+        <v>38.90219613637249</v>
       </c>
       <c r="G67">
         <v>15.5</v>
@@ -6775,28 +6775,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M67">
-        <v>2.049733137336899</v>
+        <v>2.081267493295928</v>
       </c>
       <c r="N67">
-        <v>14.69860019599644</v>
+        <v>14.66706584003741</v>
       </c>
       <c r="O67">
-        <v>4.262594056838966</v>
+        <v>4.253449093610848</v>
       </c>
       <c r="P67">
-        <v>10.43600613915747</v>
+        <v>10.41361674642656</v>
       </c>
       <c r="Q67">
-        <v>10.93600613915747</v>
+        <v>10.91361674642656</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3218686697615371</v>
+        <v>0.3289727528150941</v>
       </c>
       <c r="T67">
-        <v>1.688401617930123</v>
+        <v>1.731849305535879</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.170982372414336</v>
+        <v>8.047179609195936</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.136920835957132</v>
+        <v>0.136497387497726</v>
       </c>
       <c r="C68">
-        <v>33.84516292415527</v>
+        <v>33.48405362715651</v>
       </c>
       <c r="D68">
-        <v>57.24735906052776</v>
+        <v>57.47567697771645</v>
       </c>
       <c r="E68">
-        <v>24.35947471762629</v>
+        <v>24.94890193181376</v>
       </c>
       <c r="F68">
-        <v>38.90219613637249</v>
+        <v>39.49162335055995</v>
       </c>
       <c r="G68">
         <v>15.5</v>
@@ -6857,28 +6857,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M68">
-        <v>2.081267493295928</v>
+        <v>2.112801849254958</v>
       </c>
       <c r="N68">
-        <v>14.66706584003741</v>
+        <v>14.63553148407838</v>
       </c>
       <c r="O68">
-        <v>4.253449093610848</v>
+        <v>4.244304130382729</v>
       </c>
       <c r="P68">
-        <v>10.41361674642656</v>
+        <v>10.39122735369565</v>
       </c>
       <c r="Q68">
-        <v>10.91361674642656</v>
+        <v>10.89122735369565</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3289727528150941</v>
+        <v>0.3365073863567455</v>
       </c>
       <c r="T68">
-        <v>1.731849305535879</v>
+        <v>1.777930186329861</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>8.047179609195936</v>
+        <v>7.927072450849728</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.136497387497726</v>
+        <v>0.13607393903832</v>
       </c>
       <c r="C69">
-        <v>33.48405362715651</v>
+        <v>33.12477280956614</v>
       </c>
       <c r="D69">
-        <v>57.47567697771645</v>
+        <v>57.70582337431356</v>
       </c>
       <c r="E69">
-        <v>24.94890193181376</v>
+        <v>25.53832914600122</v>
       </c>
       <c r="F69">
-        <v>39.49162335055995</v>
+        <v>40.08105056474741</v>
       </c>
       <c r="G69">
         <v>15.5</v>
@@ -6939,28 +6939,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M69">
-        <v>2.112801849254958</v>
+        <v>2.144336205213987</v>
       </c>
       <c r="N69">
-        <v>14.63553148407838</v>
+        <v>14.60399712811935</v>
       </c>
       <c r="O69">
-        <v>4.244304130382729</v>
+        <v>4.23515916715461</v>
       </c>
       <c r="P69">
-        <v>10.39122735369565</v>
+        <v>10.36883796096474</v>
       </c>
       <c r="Q69">
-        <v>10.89122735369565</v>
+        <v>10.86883796096474</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3365073863567455</v>
+        <v>0.3445129344947501</v>
       </c>
       <c r="T69">
-        <v>1.777930186329861</v>
+        <v>1.826891122173468</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.927072450849728</v>
+        <v>7.810497855984291</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.13607393903832</v>
+        <v>0.135650490578914</v>
       </c>
       <c r="C70">
-        <v>33.12477280956614</v>
+        <v>32.76734252470136</v>
       </c>
       <c r="D70">
-        <v>57.70582337431356</v>
+        <v>57.93782030363624</v>
       </c>
       <c r="E70">
-        <v>25.53832914600122</v>
+        <v>26.12775636018868</v>
       </c>
       <c r="F70">
-        <v>40.08105056474741</v>
+        <v>40.67047777893488</v>
       </c>
       <c r="G70">
         <v>15.5</v>
@@ -7021,28 +7021,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M70">
-        <v>2.144336205213987</v>
+        <v>2.175870561173016</v>
       </c>
       <c r="N70">
-        <v>14.60399712811935</v>
+        <v>14.57246277216032</v>
       </c>
       <c r="O70">
-        <v>4.23515916715461</v>
+        <v>4.226014203926492</v>
       </c>
       <c r="P70">
-        <v>10.36883796096474</v>
+        <v>10.34644856823382</v>
       </c>
       <c r="Q70">
-        <v>10.86883796096474</v>
+        <v>10.84644856823382</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3445129344947501</v>
+        <v>0.3530349696094002</v>
       </c>
       <c r="T70">
-        <v>1.826891122173468</v>
+        <v>1.879010828071501</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.810497855984291</v>
+        <v>7.697302234883068</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.135650490578914</v>
+        <v>0.135624642119508</v>
       </c>
       <c r="C71">
-        <v>32.76734252470136</v>
+        <v>32.19213746684198</v>
       </c>
       <c r="D71">
-        <v>57.93782030363624</v>
+        <v>57.95204245996432</v>
       </c>
       <c r="E71">
-        <v>26.12775636018868</v>
+        <v>26.71718357437614</v>
       </c>
       <c r="F71">
-        <v>40.67047777893488</v>
+        <v>41.25990499312234</v>
       </c>
       <c r="G71">
         <v>15.5</v>
@@ -7103,45 +7103,45 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M71">
-        <v>2.175870561173016</v>
+        <v>2.240412841126543</v>
       </c>
       <c r="N71">
-        <v>14.57246277216032</v>
+        <v>14.50792049220679</v>
       </c>
       <c r="O71">
-        <v>4.226014203926492</v>
+        <v>4.207296942739969</v>
       </c>
       <c r="P71">
-        <v>10.34644856823382</v>
+        <v>10.30062354946682</v>
       </c>
       <c r="Q71">
-        <v>10.84644856823382</v>
+        <v>10.80062354946682</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3530349696094002</v>
+        <v>0.3621251403983602</v>
       </c>
       <c r="T71">
-        <v>1.879010828071501</v>
+        <v>1.934605181029402</v>
       </c>
       <c r="U71">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V71">
         <v>0.29</v>
       </c>
       <c r="W71">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y71">
-        <v>7.697302234883068</v>
+        <v>7.475556748242791</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.135624642119508</v>
+        <v>0.1352068736601021</v>
       </c>
       <c r="C72">
-        <v>32.19213746684198</v>
+        <v>31.83354408791696</v>
       </c>
       <c r="D72">
-        <v>57.95204245996432</v>
+        <v>58.18287629522676</v>
       </c>
       <c r="E72">
-        <v>26.71718357437614</v>
+        <v>27.3066107885636</v>
       </c>
       <c r="F72">
-        <v>41.25990499312234</v>
+        <v>41.8493322073098</v>
       </c>
       <c r="G72">
         <v>15.5</v>
@@ -7185,28 +7185,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M72">
-        <v>2.240412841126543</v>
+        <v>2.272418738856922</v>
       </c>
       <c r="N72">
-        <v>14.50792049220679</v>
+        <v>14.47591459447641</v>
       </c>
       <c r="O72">
-        <v>4.207296942739969</v>
+        <v>4.198015232398159</v>
       </c>
       <c r="P72">
-        <v>10.30062354946682</v>
+        <v>10.27789936207825</v>
       </c>
       <c r="Q72">
-        <v>10.80062354946682</v>
+        <v>10.77789936207825</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3621251403983602</v>
+        <v>0.3718422195175934</v>
       </c>
       <c r="T72">
-        <v>1.934605181029402</v>
+        <v>1.994033627294746</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.475556748242791</v>
+        <v>7.3702672165774</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1352068736601021</v>
+        <v>0.1347891052006961</v>
       </c>
       <c r="C73">
-        <v>31.83354408791695</v>
+        <v>31.47679697177026</v>
       </c>
       <c r="D73">
-        <v>58.18287629522674</v>
+        <v>58.41555639326752</v>
       </c>
       <c r="E73">
-        <v>27.3066107885636</v>
+        <v>27.89603800275106</v>
       </c>
       <c r="F73">
-        <v>41.8493322073098</v>
+        <v>42.43875942149726</v>
       </c>
       <c r="G73">
         <v>15.5</v>
@@ -7267,28 +7267,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M73">
-        <v>2.272418738856922</v>
+        <v>2.304424636587301</v>
       </c>
       <c r="N73">
-        <v>14.47591459447641</v>
+        <v>14.44390869674603</v>
       </c>
       <c r="O73">
-        <v>4.198015232398159</v>
+        <v>4.188733522056349</v>
       </c>
       <c r="P73">
-        <v>10.27789936207825</v>
+        <v>10.25517517468968</v>
       </c>
       <c r="Q73">
-        <v>10.77789936207825</v>
+        <v>10.75517517468968</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3718422195175933</v>
+        <v>0.3822533757167717</v>
       </c>
       <c r="T73">
-        <v>1.994033627294745</v>
+        <v>2.057706962579041</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.3702672165774</v>
+        <v>7.267902394124937</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1347891052006961</v>
+        <v>0.1343713367412901</v>
       </c>
       <c r="C74">
-        <v>31.47679697177026</v>
+        <v>31.12191835759866</v>
       </c>
       <c r="D74">
-        <v>58.41555639326752</v>
+        <v>58.65010499328338</v>
       </c>
       <c r="E74">
-        <v>27.89603800275106</v>
+        <v>28.48546521693852</v>
       </c>
       <c r="F74">
-        <v>42.43875942149726</v>
+        <v>43.02818663568472</v>
       </c>
       <c r="G74">
         <v>15.5</v>
@@ -7349,28 +7349,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M74">
-        <v>2.304424636587301</v>
+        <v>2.33643053431768</v>
       </c>
       <c r="N74">
-        <v>14.44390869674603</v>
+        <v>14.41190279901565</v>
       </c>
       <c r="O74">
-        <v>4.188733522056349</v>
+        <v>4.179451811714539</v>
       </c>
       <c r="P74">
-        <v>10.25517517468968</v>
+        <v>10.23245098730112</v>
       </c>
       <c r="Q74">
-        <v>10.75517517468968</v>
+        <v>10.73245098730112</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3822533757167717</v>
+        <v>0.3934357286714447</v>
       </c>
       <c r="T74">
-        <v>2.057706962579041</v>
+        <v>2.126096841217729</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.267902394124937</v>
+        <v>7.168342087356103</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1343713367412901</v>
+        <v>0.1339535682818841</v>
       </c>
       <c r="C75">
-        <v>31.12191835759866</v>
+        <v>30.7689308432156</v>
       </c>
       <c r="D75">
-        <v>58.65010499328338</v>
+        <v>58.88654469308779</v>
       </c>
       <c r="E75">
-        <v>28.48546521693852</v>
+        <v>29.07489243112599</v>
       </c>
       <c r="F75">
-        <v>43.02818663568472</v>
+        <v>43.61761384987219</v>
       </c>
       <c r="G75">
         <v>15.5</v>
@@ -7431,28 +7431,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M75">
-        <v>2.33643053431768</v>
+        <v>2.36843643204806</v>
       </c>
       <c r="N75">
-        <v>14.41190279901565</v>
+        <v>14.37989690128527</v>
       </c>
       <c r="O75">
-        <v>4.179451811714539</v>
+        <v>4.170170101372729</v>
       </c>
       <c r="P75">
-        <v>10.23245098730112</v>
+        <v>10.20972679991254</v>
       </c>
       <c r="Q75">
-        <v>10.73245098730112</v>
+        <v>10.70972679991254</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3934357286714447</v>
+        <v>0.4054782626226311</v>
       </c>
       <c r="T75">
-        <v>2.126096841217729</v>
+        <v>2.199747479751702</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>7.168342087356103</v>
+        <v>7.071472599689128</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1339535682818841</v>
+        <v>0.1335357998224781</v>
       </c>
       <c r="C76">
-        <v>30.7689308432156</v>
+        <v>30.41785739230944</v>
       </c>
       <c r="D76">
-        <v>58.88654469308779</v>
+        <v>59.12489845636908</v>
       </c>
       <c r="E76">
-        <v>29.07489243112599</v>
+        <v>29.66431964531345</v>
       </c>
       <c r="F76">
-        <v>43.61761384987219</v>
+        <v>44.20704106405964</v>
       </c>
       <c r="G76">
         <v>15.5</v>
@@ -7513,28 +7513,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M76">
-        <v>2.36843643204806</v>
+        <v>2.400442329778439</v>
       </c>
       <c r="N76">
-        <v>14.37989690128527</v>
+        <v>14.3478910035549</v>
       </c>
       <c r="O76">
-        <v>4.170170101372729</v>
+        <v>4.16088839103092</v>
       </c>
       <c r="P76">
-        <v>10.20972679991254</v>
+        <v>10.18700261252398</v>
       </c>
       <c r="Q76">
-        <v>10.70972679991254</v>
+        <v>10.68700261252398</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4054782626226311</v>
+        <v>0.4184841992899124</v>
       </c>
       <c r="T76">
-        <v>2.199747479751702</v>
+        <v>2.279290169368392</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.071472599689128</v>
+        <v>6.97718629835994</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1335357998224781</v>
+        <v>0.1331180313630721</v>
       </c>
       <c r="C77">
-        <v>30.41785739230944</v>
+        <v>30.06872134187784</v>
       </c>
       <c r="D77">
-        <v>59.12489845636908</v>
+        <v>59.36518962012495</v>
       </c>
       <c r="E77">
-        <v>29.66431964531345</v>
+        <v>30.25374685950091</v>
       </c>
       <c r="F77">
-        <v>44.20704106405964</v>
+        <v>44.79646827824711</v>
       </c>
       <c r="G77">
         <v>15.5</v>
@@ -7595,28 +7595,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M77">
-        <v>2.400442329778439</v>
+        <v>2.432448227508818</v>
       </c>
       <c r="N77">
-        <v>14.3478910035549</v>
+        <v>14.31588510582452</v>
       </c>
       <c r="O77">
-        <v>4.16088839103092</v>
+        <v>4.15160668068911</v>
       </c>
       <c r="P77">
-        <v>10.18700261252398</v>
+        <v>10.16427842513541</v>
       </c>
       <c r="Q77">
-        <v>10.68700261252398</v>
+        <v>10.66427842513541</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4184841992899124</v>
+        <v>0.4325739640128005</v>
       </c>
       <c r="T77">
-        <v>2.279290169368392</v>
+        <v>2.36546141645314</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.97718629835994</v>
+        <v>6.885381215486782</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1331180313630721</v>
+        <v>0.1327002629036661</v>
       </c>
       <c r="C78">
-        <v>30.06872134187784</v>
+        <v>29.72154640984488</v>
       </c>
       <c r="D78">
-        <v>59.36518962012495</v>
+        <v>59.60744190227944</v>
       </c>
       <c r="E78">
-        <v>30.25374685950091</v>
+        <v>30.84317407368837</v>
       </c>
       <c r="F78">
-        <v>44.79646827824711</v>
+        <v>45.38589549243457</v>
       </c>
       <c r="G78">
         <v>15.5</v>
@@ -7677,28 +7677,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M78">
-        <v>2.432448227508818</v>
+        <v>2.464454125239197</v>
       </c>
       <c r="N78">
-        <v>14.31588510582452</v>
+        <v>14.28387920809414</v>
       </c>
       <c r="O78">
-        <v>4.15160668068911</v>
+        <v>4.1423249703473</v>
       </c>
       <c r="P78">
-        <v>10.16427842513541</v>
+        <v>10.14155423774684</v>
       </c>
       <c r="Q78">
-        <v>10.66427842513541</v>
+        <v>10.64155423774684</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4325739640128005</v>
+        <v>0.4478889256681136</v>
       </c>
       <c r="T78">
-        <v>2.36546141645314</v>
+        <v>2.4591258154583</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.885381215486782</v>
+        <v>6.795960680220721</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1327002629036661</v>
+        <v>0.1322824944442601</v>
       </c>
       <c r="C79">
-        <v>29.72154640984488</v>
+        <v>29.37635670286504</v>
       </c>
       <c r="D79">
-        <v>59.60744190227944</v>
+        <v>59.85167940948708</v>
       </c>
       <c r="E79">
-        <v>30.84317407368837</v>
+        <v>31.43260128787584</v>
       </c>
       <c r="F79">
-        <v>45.38589549243457</v>
+        <v>45.97532270662204</v>
       </c>
       <c r="G79">
         <v>15.5</v>
@@ -7759,28 +7759,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M79">
-        <v>2.464454125239197</v>
+        <v>2.496460022969577</v>
       </c>
       <c r="N79">
-        <v>14.28387920809414</v>
+        <v>14.25187331036376</v>
       </c>
       <c r="O79">
-        <v>4.1423249703473</v>
+        <v>4.13304326000549</v>
       </c>
       <c r="P79">
-        <v>10.14155423774684</v>
+        <v>10.11883005035827</v>
       </c>
       <c r="Q79">
-        <v>10.64155423774684</v>
+        <v>10.61883005035827</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4478889256681136</v>
+        <v>0.4645961565648188</v>
       </c>
       <c r="T79">
-        <v>2.4591258154583</v>
+        <v>2.561305159827566</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.795960680220721</v>
+        <v>6.708832979192248</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1322824944442601</v>
+        <v>0.1318647259848542</v>
       </c>
       <c r="C80">
-        <v>29.37635670286504</v>
+        <v>29.03317672432002</v>
       </c>
       <c r="D80">
-        <v>59.85167940948708</v>
+        <v>60.09792664512951</v>
       </c>
       <c r="E80">
-        <v>31.43260128787584</v>
+        <v>32.0220285020633</v>
       </c>
       <c r="F80">
-        <v>45.97532270662204</v>
+        <v>46.5647499208095</v>
       </c>
       <c r="G80">
         <v>15.5</v>
@@ -7841,28 +7841,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M80">
-        <v>2.496460022969577</v>
+        <v>2.528465920699956</v>
       </c>
       <c r="N80">
-        <v>14.25187331036376</v>
+        <v>14.21986741263338</v>
       </c>
       <c r="O80">
-        <v>4.13304326000549</v>
+        <v>4.12376154966368</v>
       </c>
       <c r="P80">
-        <v>10.11883005035827</v>
+        <v>10.0961058629697</v>
       </c>
       <c r="Q80">
-        <v>10.61883005035827</v>
+        <v>10.5961058629697</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4645961565648188</v>
+        <v>0.4828945523088293</v>
       </c>
       <c r="T80">
-        <v>2.561305159827566</v>
+        <v>2.673215870327238</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.708832979192248</v>
+        <v>6.623911042746778</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1318647259848542</v>
+        <v>0.1314469575254481</v>
       </c>
       <c r="C81">
-        <v>29.03317672432002</v>
+        <v>28.69203138251365</v>
       </c>
       <c r="D81">
-        <v>60.09792664512951</v>
+        <v>60.3462085175106</v>
       </c>
       <c r="E81">
-        <v>32.0220285020633</v>
+        <v>32.61145571625076</v>
       </c>
       <c r="F81">
-        <v>46.5647499208095</v>
+        <v>47.15417713499696</v>
       </c>
       <c r="G81">
         <v>15.5</v>
@@ -7923,28 +7923,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M81">
-        <v>2.528465920699956</v>
+        <v>2.560471818430335</v>
       </c>
       <c r="N81">
-        <v>14.21986741263338</v>
+        <v>14.187861514903</v>
       </c>
       <c r="O81">
-        <v>4.12376154966368</v>
+        <v>4.11447983932187</v>
       </c>
       <c r="P81">
-        <v>10.0961058629697</v>
+        <v>10.07338167558113</v>
       </c>
       <c r="Q81">
-        <v>10.5961058629697</v>
+        <v>10.57338167558113</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4828945523088293</v>
+        <v>0.5030227876272408</v>
       </c>
       <c r="T81">
-        <v>2.673215870327238</v>
+        <v>2.796317651876878</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.623911042746778</v>
+        <v>6.541112154712443</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1314469575254481</v>
+        <v>0.1310291890660422</v>
       </c>
       <c r="C82">
-        <v>28.69203138251365</v>
+        <v>28.35294599907081</v>
       </c>
       <c r="D82">
-        <v>60.3462085175106</v>
+        <v>60.59655034825524</v>
       </c>
       <c r="E82">
-        <v>32.61145571625076</v>
+        <v>33.20088293043823</v>
       </c>
       <c r="F82">
-        <v>47.15417713499696</v>
+        <v>47.74360434918442</v>
       </c>
       <c r="G82">
         <v>15.5</v>
@@ -8005,28 +8005,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M82">
-        <v>2.560471818430335</v>
+        <v>2.592477716160714</v>
       </c>
       <c r="N82">
-        <v>14.187861514903</v>
+        <v>14.15585561717262</v>
       </c>
       <c r="O82">
-        <v>4.11447983932187</v>
+        <v>4.105198128980059</v>
       </c>
       <c r="P82">
-        <v>10.07338167558113</v>
+        <v>10.05065748819256</v>
       </c>
       <c r="Q82">
-        <v>10.57338167558113</v>
+        <v>10.55065748819256</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5030227876272408</v>
+        <v>0.5252697845581168</v>
       </c>
       <c r="T82">
-        <v>2.796317651876878</v>
+        <v>2.9323775156949</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.541112154712443</v>
+        <v>6.460357683666609</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1310291890660422</v>
+        <v>0.1306114206066362</v>
       </c>
       <c r="C83">
-        <v>28.35294599907081</v>
+        <v>28.01594631754649</v>
       </c>
       <c r="D83">
-        <v>60.59655034825524</v>
+        <v>60.84897788091836</v>
       </c>
       <c r="E83">
-        <v>33.20088293043823</v>
+        <v>33.79031014462569</v>
       </c>
       <c r="F83">
-        <v>47.74360434918442</v>
+        <v>48.33303156337188</v>
       </c>
       <c r="G83">
         <v>15.5</v>
@@ -8087,28 +8087,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M83">
-        <v>2.592477716160714</v>
+        <v>2.624483613891093</v>
       </c>
       <c r="N83">
-        <v>14.15585561717262</v>
+        <v>14.12384971944224</v>
       </c>
       <c r="O83">
-        <v>4.105198128980059</v>
+        <v>4.095916418638249</v>
       </c>
       <c r="P83">
-        <v>10.05065748819256</v>
+        <v>10.02793330080399</v>
       </c>
       <c r="Q83">
-        <v>10.55065748819256</v>
+        <v>10.52793330080399</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5252697845581168</v>
+        <v>0.5499886700368678</v>
       </c>
       <c r="T83">
-        <v>2.9323775156949</v>
+        <v>3.08355514215937</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.460357683666609</v>
+        <v>6.381572833865798</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1306114206066362</v>
+        <v>0.1301936521472302</v>
       </c>
       <c r="C84">
-        <v>28.01594631754649</v>
+        <v>27.68105851225045</v>
       </c>
       <c r="D84">
-        <v>60.84897788091836</v>
+        <v>61.1035172898098</v>
       </c>
       <c r="E84">
-        <v>33.79031014462569</v>
+        <v>34.37973735881315</v>
       </c>
       <c r="F84">
-        <v>48.33303156337188</v>
+        <v>48.92245877755935</v>
       </c>
       <c r="G84">
         <v>15.5</v>
@@ -8169,28 +8169,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M84">
-        <v>2.624483613891093</v>
+        <v>2.656489511621473</v>
       </c>
       <c r="N84">
-        <v>14.12384971944224</v>
+        <v>14.09184382171186</v>
       </c>
       <c r="O84">
-        <v>4.095916418638249</v>
+        <v>4.086634708296439</v>
       </c>
       <c r="P84">
-        <v>10.02793330080399</v>
+        <v>10.00520911341542</v>
       </c>
       <c r="Q84">
-        <v>10.52793330080399</v>
+        <v>10.50520911341542</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5499886700368678</v>
+        <v>0.5776156596895894</v>
       </c>
       <c r="T84">
-        <v>3.08355514215937</v>
+        <v>3.252518371737306</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.381572833865798</v>
+        <v>6.304686414180667</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1301936521472302</v>
+        <v>0.1297758836878242</v>
       </c>
       <c r="C85">
-        <v>27.68105851225045</v>
+        <v>27.34830919729485</v>
       </c>
       <c r="D85">
-        <v>61.1035172898098</v>
+        <v>61.36019518904167</v>
       </c>
       <c r="E85">
-        <v>34.37973735881315</v>
+        <v>34.96916457300061</v>
       </c>
       <c r="F85">
-        <v>48.92245877755935</v>
+        <v>49.51188599174681</v>
       </c>
       <c r="G85">
         <v>15.5</v>
@@ -8251,28 +8251,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M85">
-        <v>2.656489511621473</v>
+        <v>2.688495409351852</v>
       </c>
       <c r="N85">
-        <v>14.09184382171186</v>
+        <v>14.05983792398148</v>
       </c>
       <c r="O85">
-        <v>4.086634708296439</v>
+        <v>4.077352997954629</v>
       </c>
       <c r="P85">
-        <v>10.00520911341542</v>
+        <v>9.982484926026853</v>
       </c>
       <c r="Q85">
-        <v>10.50520911341542</v>
+        <v>10.48248492602685</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5776156596895894</v>
+        <v>0.6086960230489016</v>
       </c>
       <c r="T85">
-        <v>3.252518371737306</v>
+        <v>3.442602005012486</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.304686414180667</v>
+        <v>6.22963062353566</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1297758836878242</v>
+        <v>0.1293581152284182</v>
       </c>
       <c r="C86">
-        <v>27.34830919729487</v>
+        <v>27.01772543587057</v>
       </c>
       <c r="D86">
-        <v>61.36019518904168</v>
+        <v>61.61903864180483</v>
       </c>
       <c r="E86">
-        <v>34.9691645730006</v>
+        <v>35.55859178718807</v>
       </c>
       <c r="F86">
-        <v>49.5118859917468</v>
+        <v>50.10131320593427</v>
       </c>
       <c r="G86">
         <v>15.5</v>
@@ -8333,28 +8333,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M86">
-        <v>2.688495409351851</v>
+        <v>2.720501307082231</v>
       </c>
       <c r="N86">
-        <v>14.05983792398148</v>
+        <v>14.0278320262511</v>
       </c>
       <c r="O86">
-        <v>4.077352997954629</v>
+        <v>4.06807128761282</v>
       </c>
       <c r="P86">
-        <v>9.982484926026853</v>
+        <v>9.959760738638284</v>
       </c>
       <c r="Q86">
-        <v>10.48248492602685</v>
+        <v>10.45976073863828</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6086960230489011</v>
+        <v>0.6439204348561213</v>
       </c>
       <c r="T86">
-        <v>3.442602005012483</v>
+        <v>3.658030122724352</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.229630623535661</v>
+        <v>6.156340851494064</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1293581152284182</v>
+        <v>0.1295509467690122</v>
       </c>
       <c r="C87">
-        <v>27.01772543587057</v>
+        <v>26.30855167688627</v>
       </c>
       <c r="D87">
-        <v>61.61903864180483</v>
+        <v>61.499292097008</v>
       </c>
       <c r="E87">
-        <v>35.55859178718807</v>
+        <v>36.14801900137553</v>
       </c>
       <c r="F87">
-        <v>50.10131320593427</v>
+        <v>50.69074042012173</v>
       </c>
       <c r="G87">
         <v>15.5</v>
@@ -8415,45 +8415,45 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M87">
-        <v>2.720501307082231</v>
+        <v>2.803197945232732</v>
       </c>
       <c r="N87">
-        <v>14.0278320262511</v>
+        <v>13.9451353881006</v>
       </c>
       <c r="O87">
-        <v>4.06807128761282</v>
+        <v>4.044089262549175</v>
       </c>
       <c r="P87">
-        <v>9.959760738638284</v>
+        <v>9.901046125551428</v>
       </c>
       <c r="Q87">
-        <v>10.45976073863828</v>
+        <v>10.40104612555143</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6439204348561213</v>
+        <v>0.6841769054929443</v>
       </c>
       <c r="T87">
-        <v>3.658030122724352</v>
+        <v>3.904233685823631</v>
       </c>
       <c r="U87">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V87">
         <v>0.29</v>
       </c>
       <c r="W87">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>6.156340851494064</v>
+        <v>5.974723747859636</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1295509467690122</v>
+        <v>0.1291402783096062</v>
       </c>
       <c r="C88">
-        <v>26.30855167688627</v>
+        <v>25.97470783784521</v>
       </c>
       <c r="D88">
-        <v>61.499292097008</v>
+        <v>61.7548754721544</v>
       </c>
       <c r="E88">
-        <v>36.14801900137553</v>
+        <v>36.73744621556299</v>
       </c>
       <c r="F88">
-        <v>50.69074042012173</v>
+        <v>51.28016763430919</v>
       </c>
       <c r="G88">
         <v>15.5</v>
@@ -8497,28 +8497,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M88">
-        <v>2.803197945232732</v>
+        <v>2.835793270177298</v>
       </c>
       <c r="N88">
-        <v>13.9451353881006</v>
+        <v>13.91254006315604</v>
       </c>
       <c r="O88">
-        <v>4.044089262549175</v>
+        <v>4.03463661831525</v>
       </c>
       <c r="P88">
-        <v>9.901046125551428</v>
+        <v>9.877903444840786</v>
       </c>
       <c r="Q88">
-        <v>10.40104612555143</v>
+        <v>10.37790344484079</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6841769054929443</v>
+        <v>0.7306266793046632</v>
       </c>
       <c r="T88">
-        <v>3.904233685823631</v>
+        <v>4.188314720168952</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.974723747859636</v>
+        <v>5.906048762252054</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1291402783096062</v>
+        <v>0.1287296098502002</v>
       </c>
       <c r="C89">
-        <v>25.97470783784521</v>
+        <v>25.64299720931718</v>
       </c>
       <c r="D89">
-        <v>61.7548754721544</v>
+        <v>62.01259205781383</v>
       </c>
       <c r="E89">
-        <v>36.73744621556299</v>
+        <v>37.32687342975046</v>
       </c>
       <c r="F89">
-        <v>51.28016763430919</v>
+        <v>51.86959484849665</v>
       </c>
       <c r="G89">
         <v>15.5</v>
@@ -8579,28 +8579,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M89">
-        <v>2.835793270177298</v>
+        <v>2.868388595121865</v>
       </c>
       <c r="N89">
-        <v>13.91254006315604</v>
+        <v>13.87994473821147</v>
       </c>
       <c r="O89">
-        <v>4.03463661831525</v>
+        <v>4.025183974081326</v>
       </c>
       <c r="P89">
-        <v>9.877903444840786</v>
+        <v>9.854760764130145</v>
       </c>
       <c r="Q89">
-        <v>10.37790344484079</v>
+        <v>10.35476076413014</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7306266793046632</v>
+        <v>0.784818082085002</v>
       </c>
       <c r="T89">
-        <v>4.188314720168952</v>
+        <v>4.519742593571828</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.906048762252054</v>
+        <v>5.838934571771916</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1287296098502002</v>
+        <v>0.1283189413907942</v>
       </c>
       <c r="C90">
-        <v>25.64299720931718</v>
+        <v>25.31344661028407</v>
       </c>
       <c r="D90">
-        <v>62.01259205781383</v>
+        <v>62.27246867296819</v>
       </c>
       <c r="E90">
-        <v>37.32687342975046</v>
+        <v>37.91630064393792</v>
       </c>
       <c r="F90">
-        <v>51.86959484849665</v>
+        <v>52.45902206268411</v>
       </c>
       <c r="G90">
         <v>15.5</v>
@@ -8661,28 +8661,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M90">
-        <v>2.868388595121865</v>
+        <v>2.900983920066432</v>
       </c>
       <c r="N90">
-        <v>13.87994473821147</v>
+        <v>13.8473494132669</v>
       </c>
       <c r="O90">
-        <v>4.025183974081326</v>
+        <v>4.015731329847402</v>
       </c>
       <c r="P90">
-        <v>9.854760764130145</v>
+        <v>9.831618083419501</v>
       </c>
       <c r="Q90">
-        <v>10.35476076413014</v>
+        <v>10.3316180834195</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.784818082085002</v>
+        <v>0.8488624671890388</v>
       </c>
       <c r="T90">
-        <v>4.519742593571828</v>
+        <v>4.911430080320681</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.838934571771916</v>
+        <v>5.773328565347512</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1283189413907942</v>
+        <v>0.1279082729313882</v>
       </c>
       <c r="C91">
-        <v>25.31344661028407</v>
+        <v>24.98608331118167</v>
       </c>
       <c r="D91">
-        <v>62.27246867296819</v>
+        <v>62.53453258805325</v>
       </c>
       <c r="E91">
-        <v>37.91630064393792</v>
+        <v>38.50572785812538</v>
       </c>
       <c r="F91">
-        <v>52.45902206268411</v>
+        <v>53.04844927687158</v>
       </c>
       <c r="G91">
         <v>15.5</v>
@@ -8743,28 +8743,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M91">
-        <v>2.900983920066432</v>
+        <v>2.933579245010999</v>
       </c>
       <c r="N91">
-        <v>13.8473494132669</v>
+        <v>13.81475408832234</v>
       </c>
       <c r="O91">
-        <v>4.015731329847402</v>
+        <v>4.006278685613477</v>
       </c>
       <c r="P91">
-        <v>9.831618083419501</v>
+        <v>9.80847540270886</v>
       </c>
       <c r="Q91">
-        <v>10.3316180834195</v>
+        <v>10.30847540270886</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8488624671890388</v>
+        <v>0.9257157293138827</v>
       </c>
       <c r="T91">
-        <v>4.911430080320681</v>
+        <v>5.381455064419304</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.773328565347512</v>
+        <v>5.709180470176984</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1279082729313882</v>
+        <v>0.1274976044719823</v>
       </c>
       <c r="C92">
-        <v>24.98608331118167</v>
+        <v>24.66093504343915</v>
       </c>
       <c r="D92">
-        <v>62.53453258805325</v>
+        <v>62.79881153449818</v>
       </c>
       <c r="E92">
-        <v>38.50572785812538</v>
+        <v>39.09515507231284</v>
       </c>
       <c r="F92">
-        <v>53.04844927687158</v>
+        <v>53.63787649105904</v>
       </c>
       <c r="G92">
         <v>15.5</v>
@@ -8825,28 +8825,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M92">
-        <v>2.933579245010999</v>
+        <v>2.966174569955565</v>
       </c>
       <c r="N92">
-        <v>13.81475408832234</v>
+        <v>13.78215876337777</v>
       </c>
       <c r="O92">
-        <v>4.006278685613477</v>
+        <v>3.996826041379553</v>
       </c>
       <c r="P92">
-        <v>9.80847540270886</v>
+        <v>9.785332721998216</v>
       </c>
       <c r="Q92">
-        <v>10.30847540270886</v>
+        <v>10.28533272199822</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9257157293138827</v>
+        <v>1.019647494133137</v>
       </c>
       <c r="T92">
-        <v>5.381455064419304</v>
+        <v>5.955930044984289</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.709180470176984</v>
+        <v>5.646442223251962</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1274976044719823</v>
+        <v>0.1270869360125763</v>
       </c>
       <c r="C93">
-        <v>24.66093504343915</v>
+        <v>24.33803000926161</v>
       </c>
       <c r="D93">
-        <v>62.79881153449818</v>
+        <v>63.06533371450811</v>
       </c>
       <c r="E93">
-        <v>39.09515507231284</v>
+        <v>39.68458228650031</v>
       </c>
       <c r="F93">
-        <v>53.63787649105904</v>
+        <v>54.22730370524651</v>
       </c>
       <c r="G93">
         <v>15.5</v>
@@ -8907,28 +8907,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M93">
-        <v>2.966174569955565</v>
+        <v>2.998769894900132</v>
       </c>
       <c r="N93">
-        <v>13.78215876337777</v>
+        <v>13.7495634384332</v>
       </c>
       <c r="O93">
-        <v>3.996826041379553</v>
+        <v>3.987373397145629</v>
       </c>
       <c r="P93">
-        <v>9.785332721998216</v>
+        <v>9.762190041287575</v>
       </c>
       <c r="Q93">
-        <v>10.28533272199822</v>
+        <v>10.26219004128757</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.019647494133137</v>
+        <v>1.137062200157204</v>
       </c>
       <c r="T93">
-        <v>5.955930044984289</v>
+        <v>6.674023770690519</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.646442223251962</v>
+        <v>5.585067851260093</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1270869360125763</v>
+        <v>0.1266762675531703</v>
       </c>
       <c r="C94">
-        <v>24.33803000926161</v>
+        <v>24.01739689166256</v>
       </c>
       <c r="D94">
-        <v>63.06533371450811</v>
+        <v>63.33412781109651</v>
       </c>
       <c r="E94">
-        <v>39.68458228650031</v>
+        <v>40.27400950068777</v>
       </c>
       <c r="F94">
-        <v>54.22730370524651</v>
+        <v>54.81673091943397</v>
       </c>
       <c r="G94">
         <v>15.5</v>
@@ -8989,28 +8989,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M94">
-        <v>2.998769894900132</v>
+        <v>3.031365219844699</v>
       </c>
       <c r="N94">
-        <v>13.7495634384332</v>
+        <v>13.71696811348864</v>
       </c>
       <c r="O94">
-        <v>3.987373397145629</v>
+        <v>3.977920752911704</v>
       </c>
       <c r="P94">
-        <v>9.762190041287575</v>
+        <v>9.739047360576933</v>
       </c>
       <c r="Q94">
-        <v>10.26219004128757</v>
+        <v>10.23904736057693</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.137062200157204</v>
+        <v>1.288023965045291</v>
       </c>
       <c r="T94">
-        <v>6.674023770690519</v>
+        <v>7.597287132312815</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.585067851260093</v>
+        <v>5.525013358235791</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1266762675531703</v>
+        <v>0.1262655990937643</v>
       </c>
       <c r="C95">
-        <v>24.01739689166256</v>
+        <v>23.69906486475414</v>
       </c>
       <c r="D95">
-        <v>63.33412781109651</v>
+        <v>63.60522299837557</v>
       </c>
       <c r="E95">
-        <v>40.27400950068777</v>
+        <v>40.86343671487523</v>
       </c>
       <c r="F95">
-        <v>54.81673091943397</v>
+        <v>55.40615813362142</v>
       </c>
       <c r="G95">
         <v>15.5</v>
@@ -9071,28 +9071,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M95">
-        <v>3.031365219844699</v>
+        <v>3.063960544789265</v>
       </c>
       <c r="N95">
-        <v>13.71696811348864</v>
+        <v>13.68437278854407</v>
       </c>
       <c r="O95">
-        <v>3.977920752911704</v>
+        <v>3.96846810867778</v>
       </c>
       <c r="P95">
-        <v>9.739047360576933</v>
+        <v>9.715904679866291</v>
       </c>
       <c r="Q95">
-        <v>10.23904736057693</v>
+        <v>10.21590467986629</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.288023965045291</v>
+        <v>1.489306318229407</v>
       </c>
       <c r="T95">
-        <v>7.597287132312815</v>
+        <v>8.828304947809212</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.525013358235791</v>
+        <v>5.46623662038222</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1262655990937643</v>
+        <v>0.1258549306343583</v>
       </c>
       <c r="C96">
-        <v>23.69906486475414</v>
+        <v>23.38306360430301</v>
       </c>
       <c r="D96">
-        <v>63.60522299837557</v>
+        <v>63.8786489521119</v>
       </c>
       <c r="E96">
-        <v>40.86343671487523</v>
+        <v>41.45286392906269</v>
       </c>
       <c r="F96">
-        <v>55.40615813362142</v>
+        <v>55.99558534780889</v>
       </c>
       <c r="G96">
         <v>15.5</v>
@@ -9153,28 +9153,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M96">
-        <v>3.063960544789265</v>
+        <v>3.096555869733832</v>
       </c>
       <c r="N96">
-        <v>13.68437278854407</v>
+        <v>13.6517774635995</v>
       </c>
       <c r="O96">
-        <v>3.96846810867778</v>
+        <v>3.959015464443856</v>
       </c>
       <c r="P96">
-        <v>9.715904679866291</v>
+        <v>9.692761999155646</v>
       </c>
       <c r="Q96">
-        <v>10.21590467986629</v>
+        <v>10.19276199915565</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.489306318229407</v>
+        <v>1.771101612687169</v>
       </c>
       <c r="T96">
-        <v>8.828304947809212</v>
+        <v>10.55172988950417</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.46623662038222</v>
+        <v>5.40869728753609</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1258549306343583</v>
+        <v>0.1254442621749523</v>
       </c>
       <c r="C97">
-        <v>23.38306360430301</v>
+        <v>23.06942329855917</v>
       </c>
       <c r="D97">
-        <v>63.8786489521119</v>
+        <v>64.15443586055552</v>
       </c>
       <c r="E97">
-        <v>41.45286392906269</v>
+        <v>42.04229114325015</v>
       </c>
       <c r="F97">
-        <v>55.99558534780889</v>
+        <v>56.58501256199635</v>
       </c>
       <c r="G97">
         <v>15.5</v>
@@ -9235,28 +9235,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M97">
-        <v>3.096555869733832</v>
+        <v>3.129151194678398</v>
       </c>
       <c r="N97">
-        <v>13.6517774635995</v>
+        <v>13.61918213865494</v>
       </c>
       <c r="O97">
-        <v>3.959015464443856</v>
+        <v>3.949562820209931</v>
       </c>
       <c r="P97">
-        <v>9.692761999155646</v>
+        <v>9.669619318445005</v>
       </c>
       <c r="Q97">
-        <v>10.19276199915565</v>
+        <v>10.169619318445</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.771101612687169</v>
+        <v>2.193794554373812</v>
       </c>
       <c r="T97">
-        <v>10.55172988950417</v>
+        <v>13.1368673020466</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.40869728753609</v>
+        <v>5.352356690790923</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1254442621749523</v>
+        <v>0.1250335937155463</v>
       </c>
       <c r="C98">
-        <v>23.06942329855918</v>
+        <v>22.75817465936694</v>
       </c>
       <c r="D98">
-        <v>64.15443586055552</v>
+        <v>64.43261443555075</v>
       </c>
       <c r="E98">
-        <v>42.04229114325015</v>
+        <v>42.63171835743761</v>
       </c>
       <c r="F98">
-        <v>56.58501256199634</v>
+        <v>57.17443977618381</v>
       </c>
       <c r="G98">
         <v>15.5</v>
@@ -9317,28 +9317,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M98">
-        <v>3.129151194678398</v>
+        <v>3.161746519622965</v>
       </c>
       <c r="N98">
-        <v>13.61918213865494</v>
+        <v>13.58658681371037</v>
       </c>
       <c r="O98">
-        <v>3.949562820209931</v>
+        <v>3.940110175976007</v>
       </c>
       <c r="P98">
-        <v>9.669619318445005</v>
+        <v>9.646476637734363</v>
       </c>
       <c r="Q98">
-        <v>10.169619318445</v>
+        <v>10.14647663773436</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.193794554373806</v>
+        <v>2.898282790518209</v>
       </c>
       <c r="T98">
-        <v>13.13686730204657</v>
+        <v>17.44542965628394</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.352356690790923</v>
+        <v>5.297177755834316</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1250335937155463</v>
+        <v>0.1246229252561403</v>
       </c>
       <c r="C99">
-        <v>22.75817465936694</v>
+        <v>22.44934893356617</v>
       </c>
       <c r="D99">
-        <v>64.43261443555075</v>
+        <v>64.71321592393744</v>
       </c>
       <c r="E99">
-        <v>42.63171835743761</v>
+        <v>43.22114557162507</v>
       </c>
       <c r="F99">
-        <v>57.17443977618381</v>
+        <v>57.76386699037127</v>
       </c>
       <c r="G99">
         <v>15.5</v>
@@ -9399,28 +9399,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M99">
-        <v>3.161746519622965</v>
+        <v>3.194341844567531</v>
       </c>
       <c r="N99">
-        <v>13.58658681371037</v>
+        <v>13.5539914887658</v>
       </c>
       <c r="O99">
-        <v>3.940110175976007</v>
+        <v>3.930657531742082</v>
       </c>
       <c r="P99">
-        <v>9.646476637734363</v>
+        <v>9.623333957023721</v>
       </c>
       <c r="Q99">
-        <v>10.14647663773436</v>
+        <v>10.12333395702372</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.898282790518209</v>
+        <v>4.307259262807014</v>
       </c>
       <c r="T99">
-        <v>17.44542965628394</v>
+        <v>26.06255436475869</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.297177755834316</v>
+        <v>5.243124921591108</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1246229252561403</v>
+        <v>0.1242122567967344</v>
       </c>
       <c r="C100">
-        <v>22.44934893356617</v>
+        <v>22.14297791469249</v>
       </c>
       <c r="D100">
-        <v>64.71321592393744</v>
+        <v>64.99627211925123</v>
       </c>
       <c r="E100">
-        <v>43.22114557162507</v>
+        <v>43.81057278581254</v>
       </c>
       <c r="F100">
-        <v>57.76386699037127</v>
+        <v>58.35329420455874</v>
       </c>
       <c r="G100">
         <v>15.5</v>
@@ -9481,28 +9481,28 @@
         <v>16.74833333333333</v>
       </c>
       <c r="M100">
-        <v>3.194341844567531</v>
+        <v>3.226937169512098</v>
       </c>
       <c r="N100">
-        <v>13.5539914887658</v>
+        <v>13.52139616382124</v>
       </c>
       <c r="O100">
-        <v>3.930657531742082</v>
+        <v>3.921204887508158</v>
       </c>
       <c r="P100">
-        <v>9.623333957023721</v>
+        <v>9.600191276313078</v>
       </c>
       <c r="Q100">
-        <v>10.12333395702372</v>
+        <v>10.10019127631308</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.307259262807014</v>
+        <v>8.534188679673429</v>
       </c>
       <c r="T100">
-        <v>26.06255436475869</v>
+        <v>51.91392849018292</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.243124921591108</v>
+        <v>5.190164063797259</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1242122567967344</v>
-      </c>
-      <c r="C101">
-        <v>22.14297791469249</v>
-      </c>
-      <c r="D101">
-        <v>64.99627211925123</v>
-      </c>
-      <c r="E101">
-        <v>43.81057278581254</v>
-      </c>
-      <c r="F101">
-        <v>58.35329420455874</v>
-      </c>
-      <c r="G101">
-        <v>15.5</v>
-      </c>
-      <c r="H101">
-        <v>44.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.24833333333333</v>
-      </c>
-      <c r="K101">
-        <v>0.5</v>
-      </c>
-      <c r="L101">
-        <v>16.74833333333333</v>
-      </c>
-      <c r="M101">
-        <v>3.226937169512098</v>
-      </c>
-      <c r="N101">
-        <v>13.52139616382124</v>
-      </c>
-      <c r="O101">
-        <v>3.921204887508158</v>
-      </c>
-      <c r="P101">
-        <v>9.600191276313078</v>
-      </c>
-      <c r="Q101">
-        <v>10.10019127631308</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.534188679673429</v>
-      </c>
-      <c r="T101">
-        <v>51.91392849018292</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.29</v>
-      </c>
-      <c r="W101">
-        <v>0.039263</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.190164063797259</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
